--- a/templates/office/EMP_DEG_091_클라우드인프라_및_방화벽신청서.xlsx
+++ b/templates/office/EMP_DEG_091_클라우드인프라_및_방화벽신청서.xlsx
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B3" s="99" t="inlineStr">
         <is>
-          <t>SyncGuard AI (화장품 표시광고 AI 자동 심의 시스템 구축)</t>
+          <t>SyncGuard AI (제품 표시·광고 AI 자동 심의 시스템 구축)</t>
         </is>
       </c>
       <c r="E3" s="101" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="C6" s="26" t="inlineStr">
         <is>
-          <t>김경호</t>
+          <t>한승우</t>
         </is>
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>한빛글로벌</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="C7" s="97" t="inlineStr">
         <is>
-          <t>서현규</t>
+          <t>임도현</t>
         </is>
       </c>
       <c r="D7" s="98" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>한빛글로벌</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="C10" s="43" t="inlineStr">
         <is>
-          <t>김재은</t>
+          <t>김태윤</t>
         </is>
       </c>
       <c r="D10" s="51" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="C11" s="52" t="inlineStr">
         <is>
-          <t>오병문 / 장지용</t>
+          <t>박준혁 / 최현우</t>
         </is>
       </c>
       <c r="D11" s="53" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="D34" s="45" t="inlineStr">
         <is>
-          <t>티움넷(MarketingHub) 연계 서버 IP 단독</t>
+          <t>마케팅허브(MarketingHub) 연계 서버 IP 단독</t>
         </is>
       </c>
       <c r="E34" s="122" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="I34" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 전용 ALB 인바운드] 티움넷 서버만 단독 오픈하여 접근 통제 (일반 사용자대역 차단, 대외연계 API :18085 전용)</t>
+          <t>[대외연계 전용 ALB 인바운드] 마케팅허브 서버만 단독 오픈하여 접근 통제 (일반 사용자대역 차단, 대외연계 API :18085 전용)</t>
         </is>
       </c>
       <c r="J34" s="124" t="n">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="I37" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 ALB ➔ 연계API] 티움넷 전용 ALB에서 대외연계 API 서버(server-api :18085, /ext-api/v1/**) 단독 라우팅</t>
+          <t>[대외연계 ALB ➔ 연계API] 마케팅허브 전용 ALB에서 대외연계 API 서버(server-api :18085, /ext-api/v1/**) 단독 라우팅</t>
         </is>
       </c>
       <c r="J37" s="124" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="I38" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 ➔ Agent 호출] 티움넷 심의 의뢰 접수 시 EKS K8s Service를 통해 AI 에이전트(:18083, OpenCV 영상 피크프레임 1차 자동추출 및 심의) 호출</t>
+          <t>[대외연계 ➔ Agent 호출] 마케팅허브 심의 의뢰 접수 시 EKS K8s Service를 통해 AI 에이전트(:18083, OpenCV 영상 피크프레임 1차 자동추출 및 심의) 호출</t>
         </is>
       </c>
       <c r="J38" s="124" t="n">
@@ -4378,7 +4378,7 @@
       <c r="F47" s="123" t="inlineStr">
         <is>
           <t>https://mkthub-api.hanbitglobal.com
-(티움넷 사내 연계 API 서버)</t>
+(마케팅허브 사내 연계 API 서버)</t>
         </is>
       </c>
       <c r="G47" s="122" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I47" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 티움넷 콜백] AI 1차 심의 완료 및 RA 최종 확정 결과(HTML 리포트 요약 + JSON) 티움넷 웹훅(Callback) 송신</t>
+          <t>[사내 Outbound - 마케팅허브 콜백] AI 1차 심의 완료 및 RA 최종 확정 결과(HTML 리포트 요약 + JSON) 마케팅허브 웹훅(Callback) 송신</t>
         </is>
       </c>
       <c r="J47" s="124" t="n">
@@ -4435,7 +4435,7 @@
       <c r="F48" s="123" t="inlineStr">
         <is>
           <t>mkthub-db.hanbitglobal.com
-(티움넷 DB 및 첨부파일 서버)</t>
+(마케팅허브 DB 및 첨부파일 서버)</t>
         </is>
       </c>
       <c r="G48" s="122" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="I48" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 티움넷 DB/파일] 티움넷 심의 의뢰 메타데이터 조회 및 대용량 첨부 시안·영상 파일 다운로드 연동</t>
+          <t>[사내 Outbound - 마케팅허브 DB/파일] 마케팅허브 심의 의뢰 메타데이터 조회 및 대용량 첨부 시안·영상 파일 다운로드 연동</t>
         </is>
       </c>
       <c r="J48" s="124" t="n">
@@ -4492,7 +4492,7 @@
       <c r="F49" s="123" t="inlineStr">
         <is>
           <t>https://productlab-core.hanbitglobal.com
-(마이비커 사내 연계 API 서버)</t>
+(프로덕트랩 사내 연계 API 서버)</t>
         </is>
       </c>
       <c r="G49" s="122" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I49" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 마이비커 API] 매일 02:00 일배치 전성분·배합한도·임상보고서 증분 수집 및 심의 시 실시간 단건 조회</t>
+          <t>[사내 Outbound - 프로덕트랩 API] 매일 02:00 일배치 전성분·배합한도·임상보고서 증분 수집 및 심의 시 실시간 단건 조회</t>
         </is>
       </c>
       <c r="J49" s="124" t="n">
@@ -4549,7 +4549,7 @@
       <c r="F50" s="123" t="inlineStr">
         <is>
           <t>productlab-db.hanbitglobal.com
-(마이비커 실증 DB 뷰)</t>
+(프로덕트랩 실증 DB 뷰)</t>
         </is>
       </c>
       <c r="G50" s="122" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="I50" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 마이비커 DB] 마이비커 전성분·처방·기술원 인체적용시험 실증보고서 뷰(View) 일배치 대량 동기화</t>
+          <t>[사내 Outbound - 프로덕트랩 DB] 프로덕트랩 전성분·처방·기술원 인체적용시험 실증보고서 뷰(View) 일배치 대량 동기화</t>
         </is>
       </c>
       <c r="J50" s="124" t="n">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="I53" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 선택 과업] 매일 02:30 식약처 화장품법·고시·가이드라인 개정본(Diff) 자동 수집 연동</t>
+          <t>[사내 Outbound - 선택 과업] 매일 02:30 식약처 표시·광고 공정화법·고시·가이드라인 개정본(Diff) 자동 수집 연동</t>
         </is>
       </c>
       <c r="J53" s="124" t="n">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="D34" s="45" t="inlineStr">
         <is>
-          <t>티움넷(MarketingHub) 연계 서버 IP 단독</t>
+          <t>마케팅허브(MarketingHub) 연계 서버 IP 단독</t>
         </is>
       </c>
       <c r="E34" s="122" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="I34" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 전용 ALB 인바운드] 티움넷 서버만 단독 오픈하여 접근 통제 (일반 사용자대역 차단, 대외연계 API :18085 전용)</t>
+          <t>[대외연계 전용 ALB 인바운드] 마케팅허브 서버만 단독 오픈하여 접근 통제 (일반 사용자대역 차단, 대외연계 API :18085 전용)</t>
         </is>
       </c>
       <c r="J34" s="124" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="I37" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 ALB ➔ 연계API] 티움넷 전용 ALB에서 대외연계 API 서버(server-api :18085, /ext-api/v1/**) 단독 라우팅</t>
+          <t>[대외연계 ALB ➔ 연계API] 마케팅허브 전용 ALB에서 대외연계 API 서버(server-api :18085, /ext-api/v1/**) 단독 라우팅</t>
         </is>
       </c>
       <c r="J37" s="124" t="n">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="I38" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 ➔ Agent 호출] 티움넷 심의 의뢰 접수 시 EKS K8s Service를 통해 AI 에이전트(:18083, OpenCV 영상 피크프레임 1차 자동추출 및 심의) 호출</t>
+          <t>[대외연계 ➔ Agent 호출] 마케팅허브 심의 의뢰 접수 시 EKS K8s Service를 통해 AI 에이전트(:18083, OpenCV 영상 피크프레임 1차 자동추출 및 심의) 호출</t>
         </is>
       </c>
       <c r="J38" s="124" t="n">
@@ -6300,7 +6300,7 @@
       <c r="F47" s="123" t="inlineStr">
         <is>
           <t>https://mkthub-api.hanbitglobal.com
-(티움넷 사내 연계 API 서버)</t>
+(마케팅허브 사내 연계 API 서버)</t>
         </is>
       </c>
       <c r="G47" s="122" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="I47" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 티움넷 콜백] AI 1차 심의 완료 및 RA 최종 확정 결과(HTML 리포트 요약 + JSON) 티움넷 웹훅(Callback) 송신</t>
+          <t>[사내 Outbound - 마케팅허브 콜백] AI 1차 심의 완료 및 RA 최종 확정 결과(HTML 리포트 요약 + JSON) 마케팅허브 웹훅(Callback) 송신</t>
         </is>
       </c>
       <c r="J47" s="124" t="n">
@@ -6357,7 +6357,7 @@
       <c r="F48" s="123" t="inlineStr">
         <is>
           <t>mkthub-db.hanbitglobal.com
-(티움넷 DB 및 첨부파일 서버)</t>
+(마케팅허브 DB 및 첨부파일 서버)</t>
         </is>
       </c>
       <c r="G48" s="122" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="I48" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 티움넷 DB/파일] 티움넷 심의 의뢰 메타데이터 조회 및 대용량 첨부 시안·영상 파일 다운로드 연동</t>
+          <t>[사내 Outbound - 마케팅허브 DB/파일] 마케팅허브 심의 의뢰 메타데이터 조회 및 대용량 첨부 시안·영상 파일 다운로드 연동</t>
         </is>
       </c>
       <c r="J48" s="124" t="n">
@@ -6414,7 +6414,7 @@
       <c r="F49" s="123" t="inlineStr">
         <is>
           <t>https://productlab-core.hanbitglobal.com
-(마이비커 사내 연계 API 서버)</t>
+(프로덕트랩 사내 연계 API 서버)</t>
         </is>
       </c>
       <c r="G49" s="122" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="I49" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 마이비커 API] 매일 02:00 일배치 전성분·배합한도·임상보고서 증분 수집 및 심의 시 실시간 단건 조회</t>
+          <t>[사내 Outbound - 프로덕트랩 API] 매일 02:00 일배치 전성분·배합한도·임상보고서 증분 수집 및 심의 시 실시간 단건 조회</t>
         </is>
       </c>
       <c r="J49" s="124" t="n">
@@ -6471,7 +6471,7 @@
       <c r="F50" s="123" t="inlineStr">
         <is>
           <t>productlab-db.hanbitglobal.com
-(마이비커 실증 DB 뷰)</t>
+(프로덕트랩 실증 DB 뷰)</t>
         </is>
       </c>
       <c r="G50" s="122" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="I50" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 마이비커 DB] 마이비커 전성분·처방·기술원 인체적용시험 실증보고서 뷰(View) 일배치 대량 동기화</t>
+          <t>[사내 Outbound - 프로덕트랩 DB] 프로덕트랩 전성분·처방·기술원 인체적용시험 실증보고서 뷰(View) 일배치 대량 동기화</t>
         </is>
       </c>
       <c r="J50" s="124" t="n">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="I53" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 선택 과업] 매일 02:30 식약처 화장품법·고시·가이드라인 개정본(Diff) 자동 수집 연동</t>
+          <t>[사내 Outbound - 선택 과업] 매일 02:30 식약처 표시·광고 공정화법·고시·가이드라인 개정본(Diff) 자동 수집 연동</t>
         </is>
       </c>
       <c r="J53" s="124" t="n">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="D34" s="45" t="inlineStr">
         <is>
-          <t>티움넷(MarketingHub) 연계 서버 IP 단독</t>
+          <t>마케팅허브(MarketingHub) 연계 서버 IP 단독</t>
         </is>
       </c>
       <c r="E34" s="122" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="I34" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 전용 ALB 인바운드] 티움넷 서버만 단독 오픈하여 접근 통제 (일반 사용자대역 차단, 대외연계 API :18085 전용)</t>
+          <t>[대외연계 전용 ALB 인바운드] 마케팅허브 서버만 단독 오픈하여 접근 통제 (일반 사용자대역 차단, 대외연계 API :18085 전용)</t>
         </is>
       </c>
       <c r="J34" s="124" t="n">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="I37" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 ALB ➔ 연계API] 티움넷 전용 ALB에서 대외연계 API 서버(server-api :18085, /ext-api/v1/**) 단독 라우팅</t>
+          <t>[대외연계 ALB ➔ 연계API] 마케팅허브 전용 ALB에서 대외연계 API 서버(server-api :18085, /ext-api/v1/**) 단독 라우팅</t>
         </is>
       </c>
       <c r="J37" s="124" t="n">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="I38" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 ➔ Agent 호출] 티움넷 심의 의뢰 접수 시 EKS K8s Service를 통해 AI 에이전트(:18083, OpenCV 영상 피크프레임 1차 자동추출 및 심의) 호출</t>
+          <t>[대외연계 ➔ Agent 호출] 마케팅허브 심의 의뢰 접수 시 EKS K8s Service를 통해 AI 에이전트(:18083, OpenCV 영상 피크프레임 1차 자동추출 및 심의) 호출</t>
         </is>
       </c>
       <c r="J38" s="124" t="n">
@@ -8222,7 +8222,7 @@
       <c r="F47" s="123" t="inlineStr">
         <is>
           <t>https://mkthub-api.hanbitglobal.com
-(티움넷 사내 연계 API 서버)</t>
+(마케팅허브 사내 연계 API 서버)</t>
         </is>
       </c>
       <c r="G47" s="122" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="I47" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 티움넷 콜백] AI 1차 심의 완료 및 RA 최종 확정 결과(HTML 리포트 요약 + JSON) 티움넷 웹훅(Callback) 송신</t>
+          <t>[사내 Outbound - 마케팅허브 콜백] AI 1차 심의 완료 및 RA 최종 확정 결과(HTML 리포트 요약 + JSON) 마케팅허브 웹훅(Callback) 송신</t>
         </is>
       </c>
       <c r="J47" s="124" t="n">
@@ -8279,7 +8279,7 @@
       <c r="F48" s="123" t="inlineStr">
         <is>
           <t>mkthub-db.hanbitglobal.com
-(티움넷 DB 및 첨부파일 서버)</t>
+(마케팅허브 DB 및 첨부파일 서버)</t>
         </is>
       </c>
       <c r="G48" s="122" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="I48" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 티움넷 DB/파일] 티움넷 심의 의뢰 메타데이터 조회 및 대용량 첨부 시안·영상 파일 다운로드 연동</t>
+          <t>[사내 Outbound - 마케팅허브 DB/파일] 마케팅허브 심의 의뢰 메타데이터 조회 및 대용량 첨부 시안·영상 파일 다운로드 연동</t>
         </is>
       </c>
       <c r="J48" s="124" t="n">
@@ -8336,7 +8336,7 @@
       <c r="F49" s="123" t="inlineStr">
         <is>
           <t>https://productlab-core.hanbitglobal.com
-(마이비커 사내 연계 API 서버)</t>
+(프로덕트랩 사내 연계 API 서버)</t>
         </is>
       </c>
       <c r="G49" s="122" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="I49" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 마이비커 API] 매일 02:00 일배치 전성분·배합한도·임상보고서 증분 수집 및 심의 시 실시간 단건 조회</t>
+          <t>[사내 Outbound - 프로덕트랩 API] 매일 02:00 일배치 전성분·배합한도·임상보고서 증분 수집 및 심의 시 실시간 단건 조회</t>
         </is>
       </c>
       <c r="J49" s="124" t="n">
@@ -8393,7 +8393,7 @@
       <c r="F50" s="123" t="inlineStr">
         <is>
           <t>productlab-db.hanbitglobal.com
-(마이비커 실증 DB 뷰)</t>
+(프로덕트랩 실증 DB 뷰)</t>
         </is>
       </c>
       <c r="G50" s="122" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="I50" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 마이비커 DB] 마이비커 전성분·처방·기술원 인체적용시험 실증보고서 뷰(View) 일배치 대량 동기화</t>
+          <t>[사내 Outbound - 프로덕트랩 DB] 프로덕트랩 전성분·처방·기술원 인체적용시험 실증보고서 뷰(View) 일배치 대량 동기화</t>
         </is>
       </c>
       <c r="J50" s="124" t="n">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="I53" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 선택 과업] 매일 02:30 식약처 화장품법·고시·가이드라인 개정본(Diff) 자동 수집 연동</t>
+          <t>[사내 Outbound - 선택 과업] 매일 02:30 식약처 표시·광고 공정화법·고시·가이드라인 개정본(Diff) 자동 수집 연동</t>
         </is>
       </c>
       <c r="J53" s="124" t="n">
@@ -10336,7 +10336,7 @@
         <is>
           <t>• [물리적 ALB 분리 ① - BO 전용 ALB] 사용자대역(사내 PC/VPN :443) 오픈 ➔ 통합웹(:3104) 및 업무서버(:18080) 라우팅
 • [BO ➔ Agent 호출] 웹 화면에서 영상 장면 추가/편집/삭제 후 재분석 요청 시 업무서버(:18080)에서 EKS K8s Service(http://syncguard-ai-agent-svc:18083)로 AI 에이전트 호출
-• 사내 Outbound :443/587 허용: SSO/IAM(sso.hanbitglobal.com), 티움넷, 마이비커, SMTP(:587)</t>
+• 사내 Outbound :443/587 허용: SSO/IAM(sso.hanbitglobal.com), 마케팅허브, 프로덕트랩, SMTP(:587)</t>
         </is>
       </c>
       <c r="J2" s="61" t="inlineStr">
@@ -10377,7 +10377,7 @@
       <c r="F3" s="60" t="inlineStr">
         <is>
           <t>• 대외연계 API(server-api :18085): OpenJDK 21, Spring Boot 3.3.5
-• 티움넷 심의 의뢰 수신 및 결과(HTML/JSON) 웹훅 콜백 회신
+• 마케팅허브 심의 의뢰 수신 및 결과(HTML/JSON) 웹훅 콜백 회신
 • 300MB 대용량 시안·동영상 S3 멀티파트 스트리밍 업로드 전담</t>
         </is>
       </c>
@@ -10397,14 +10397,14 @@
       </c>
       <c r="I3" s="60" t="inlineStr">
         <is>
-          <t>• [물리적 ALB 분리 ② - 대외연계 전용 ALB] 티움넷(MarketingHub) 서버 IP만 단독 오픈(:443)하여 접근 통제 분리 (일반 사용자대역 접근 차단)
+          <t>• [물리적 ALB 분리 ② - 대외연계 전용 ALB] 마케팅허브(MarketingHub) 서버 IP만 단독 오픈(:443)하여 접근 통제 분리 (일반 사용자대역 접근 차단)
 • [대외연계 ➔ Agent 호출] 심의 의뢰 접수 시 대외연계 서버(:18085)에서 EKS K8s Service(http://syncguard-ai-agent-svc:18083)를 통해 AI 에이전트 호출
 • 300MB 대용량 업로드 대응: ALB Idle Timeout 300초, Max Body Size 350MB 설정</t>
         </is>
       </c>
       <c r="J3" s="61" t="inlineStr">
         <is>
-          <t>티움넷만 오픈(접근통제)
+          <t>마케팅허브만 오픈(접근통제)
 대외연계 ALB 물리 분리</t>
         </is>
       </c>
@@ -10505,7 +10505,7 @@
       <c r="F5" s="60" t="inlineStr">
         <is>
           <t>• OpenJDK 21, Spring Boot 3.3.5 + Spring Scheduler (:18084)
-• 매일 02:00 마이비커(ProductLab) 전성분·배합한도·임상보고서 증분 수집
+• 매일 02:00 프로덕트랩(ProductLab) 전성분·배합한도·임상보고서 증분 수집
 • [Option] 매일 02:30 KT 레몬 식약처 법령·가이드라인 개정본(Diff) 수집</t>
         </is>
       </c>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="I5" s="60" t="inlineStr">
         <is>
-          <t>• 사내 Outbound 오픈: 마이비커 API(https://productlab-core.hanbitglobal.com:443) 및 DB(:1521/5432), 티움넷 DB, [Option] KT 레몬(https://ktlemon-gw.hanbitglobal.com:443)
+          <t>• 사내 Outbound 오픈: 프로덕트랩 API(https://productlab-core.hanbitglobal.com:443) 및 DB(:1521/5432), 마케팅허브 DB, [Option] KT 레몬(https://ktlemon-gw.hanbitglobal.com:443)
 • 신규 수집 문서 청킹·벡터 색인 시 EKS K8s Service로 AI 에이전트(:18083) 호출</t>
         </is>
       </c>
@@ -10703,7 +10703,7 @@
         <is>
           <t>• [물리적 ALB 분리 ① - BO 전용 ALB] 사용자대역(사내 PC/VPN :443) 오픈 ➔ 통합웹(:3104) 및 업무서버(:18080) 라우팅
 • [BO ➔ Agent 호출] 웹 화면에서 영상 장면 추가/편집/삭제 후 재분석 요청 시 업무서버(:18080)에서 EKS K8s Service(http://syncguard-ai-agent-svc:18083)로 AI 에이전트 호출
-• 사내 Outbound :443/587 허용: SSO/IAM(sso.hanbitglobal.com), 티움넷, 마이비커, SMTP(:587)</t>
+• 사내 Outbound :443/587 허용: SSO/IAM(sso.hanbitglobal.com), 마케팅허브, 프로덕트랩, SMTP(:587)</t>
         </is>
       </c>
       <c r="J8" s="61" t="inlineStr">
@@ -10744,7 +10744,7 @@
       <c r="F9" s="60" t="inlineStr">
         <is>
           <t>DEV 동일
-(티움넷 검증계 연동)</t>
+(마케팅허브 검증계 연동)</t>
         </is>
       </c>
       <c r="G9" s="61" t="inlineStr">
@@ -10763,14 +10763,14 @@
       </c>
       <c r="I9" s="60" t="inlineStr">
         <is>
-          <t>• [물리적 ALB 분리 ② - 대외연계 전용 ALB] 티움넷(MarketingHub) 서버 IP만 단독 오픈(:443)하여 접근 통제 분리 (일반 사용자대역 접근 차단)
+          <t>• [물리적 ALB 분리 ② - 대외연계 전용 ALB] 마케팅허브(MarketingHub) 서버 IP만 단독 오픈(:443)하여 접근 통제 분리 (일반 사용자대역 접근 차단)
 • [대외연계 ➔ Agent 호출] 심의 의뢰 접수 시 대외연계 서버(:18085)에서 EKS K8s Service(http://syncguard-ai-agent-svc:18083)를 통해 AI 에이전트 호출
 • 300MB 대용량 업로드 대응: ALB Idle Timeout 300초, Max Body Size 350MB 설정</t>
         </is>
       </c>
       <c r="J9" s="61" t="inlineStr">
         <is>
-          <t>티움넷만 오픈(접근통제)
+          <t>마케팅허브만 오픈(접근통제)
 대외연계 ALB 물리 분리</t>
         </is>
       </c>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="I11" s="60" t="inlineStr">
         <is>
-          <t>• 사내 Outbound 오픈: 마이비커 API(https://productlab-core.hanbitglobal.com:443) 및 DB(:1521/5432), 티움넷 DB, [Option] KT 레몬(https://ktlemon-gw.hanbitglobal.com:443)
+          <t>• 사내 Outbound 오픈: 프로덕트랩 API(https://productlab-core.hanbitglobal.com:443) 및 DB(:1521/5432), 마케팅허브 DB, [Option] KT 레몬(https://ktlemon-gw.hanbitglobal.com:443)
 • 신규 수집 문서 청킹·벡터 색인 시 EKS K8s Service로 AI 에이전트(:18083) 호출</t>
         </is>
       </c>
@@ -11065,7 +11065,7 @@
         <is>
           <t>• [물리적 ALB 분리 ① - BO 전용 ALB] 사용자대역(사내 PC/VPN :443) 오픈 ➔ 통합웹(:3104) 및 업무서버(:18080) 라우팅
 • [BO ➔ Agent 호출] 웹 화면에서 영상 장면 추가/편집/삭제 후 재분석 요청 시 업무서버(:18080)에서 EKS K8s Service(http://syncguard-ai-agent-svc:18083)로 AI 에이전트 호출
-• 사내 Outbound :443/587 허용: SSO/IAM(sso.hanbitglobal.com), 티움넷, 마이비커, SMTP(:587)</t>
+• 사내 Outbound :443/587 허용: SSO/IAM(sso.hanbitglobal.com), 마케팅허브, 프로덕트랩, SMTP(:587)</t>
         </is>
       </c>
       <c r="J14" s="61" t="inlineStr">
@@ -11125,14 +11125,14 @@
       </c>
       <c r="I15" s="60" t="inlineStr">
         <is>
-          <t>• [물리적 ALB 분리 ② - 대외연계 전용 ALB] 티움넷(MarketingHub) 서버 IP만 단독 오픈(:443)하여 접근 통제 분리 (일반 사용자대역 접근 차단)
+          <t>• [물리적 ALB 분리 ② - 대외연계 전용 ALB] 마케팅허브(MarketingHub) 서버 IP만 단독 오픈(:443)하여 접근 통제 분리 (일반 사용자대역 접근 차단)
 • [대외연계 ➔ Agent 호출] 심의 의뢰 접수 시 대외연계 서버(:18085)에서 EKS K8s Service(http://syncguard-ai-agent-svc:18083)를 통해 AI 에이전트 호출
 • 300MB 대용량 업로드 대응: ALB Idle Timeout 300초, Max Body Size 350MB 설정</t>
         </is>
       </c>
       <c r="J15" s="61" t="inlineStr">
         <is>
-          <t>티움넷만 오픈(접근통제)
+          <t>마케팅허브만 오픈(접근통제)
 대외연계 ALB 물리 분리</t>
         </is>
       </c>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="I17" s="60" t="inlineStr">
         <is>
-          <t>• 사내 Outbound 오픈: 마이비커 API(https://productlab-core.hanbitglobal.com:443) 및 DB(:1521/5432), 티움넷 DB, [Option] KT 레몬(https://ktlemon-gw.hanbitglobal.com:443)
+          <t>• 사내 Outbound 오픈: 프로덕트랩 API(https://productlab-core.hanbitglobal.com:443) 및 DB(:1521/5432), 마케팅허브 DB, [Option] KT 레몬(https://ktlemon-gw.hanbitglobal.com:443)
 • 신규 수집 문서 청킹·벡터 색인 시 EKS K8s Service로 AI 에이전트(:18083) 호출</t>
         </is>
       </c>
@@ -11794,7 +11794,7 @@
     <row r="3">
       <c r="A3" s="129" t="inlineStr">
         <is>
-          <t>김재은</t>
+          <t>김태윤</t>
         </is>
       </c>
       <c r="B3" s="130" t="inlineStr">
@@ -11858,7 +11858,7 @@
     <row r="4">
       <c r="A4" s="129" t="inlineStr">
         <is>
-          <t>김재은</t>
+          <t>김태윤</t>
         </is>
       </c>
       <c r="B4" s="130" t="inlineStr">
@@ -11921,7 +11921,7 @@
     <row r="5">
       <c r="A5" s="129" t="inlineStr">
         <is>
-          <t>김재은</t>
+          <t>김태윤</t>
         </is>
       </c>
       <c r="B5" s="130" t="inlineStr">
@@ -11984,7 +11984,7 @@
     <row r="6">
       <c r="A6" s="129" t="inlineStr">
         <is>
-          <t>오병문</t>
+          <t>박준혁</t>
         </is>
       </c>
       <c r="B6" s="130" t="inlineStr">
@@ -12051,7 +12051,7 @@
     <row r="7">
       <c r="A7" s="129" t="inlineStr">
         <is>
-          <t>오병문</t>
+          <t>박준혁</t>
         </is>
       </c>
       <c r="B7" s="130" t="inlineStr">
@@ -12118,7 +12118,7 @@
     <row r="8">
       <c r="A8" s="129" t="inlineStr">
         <is>
-          <t>오병문</t>
+          <t>박준혁</t>
         </is>
       </c>
       <c r="B8" s="130" t="inlineStr">
@@ -12181,7 +12181,7 @@
     <row r="9">
       <c r="A9" s="129" t="inlineStr">
         <is>
-          <t>장지용</t>
+          <t>최현우</t>
         </is>
       </c>
       <c r="B9" s="130" t="inlineStr">
@@ -12248,7 +12248,7 @@
     <row r="10">
       <c r="A10" s="129" t="inlineStr">
         <is>
-          <t>장지용</t>
+          <t>최현우</t>
         </is>
       </c>
       <c r="B10" s="130" t="inlineStr">
@@ -12315,7 +12315,7 @@
     <row r="11">
       <c r="A11" s="129" t="inlineStr">
         <is>
-          <t>장지용</t>
+          <t>최현우</t>
         </is>
       </c>
       <c r="B11" s="130" t="inlineStr">

--- a/templates/office/EMP_DEG_091_클라우드인프라_및_방화벽신청서.xlsx
+++ b/templates/office/EMP_DEG_091_클라우드인프라_및_방화벽신청서.xlsx
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B3" s="99" t="inlineStr">
         <is>
-          <t>SyncGuard AI (제품 표시·광고 AI 자동 심의 시스템 구축)</t>
+          <t>SyncFlow AI (구매계약·기술규격 AI 자동 검증 시스템 구축)</t>
         </is>
       </c>
       <c r="E3" s="101" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="I40" s="65" t="inlineStr">
         <is>
-          <t>[P1] CIR — 화장품 성분 독성 리뷰</t>
+          <t>[P1] CIR — 전장부품 성분 독성 리뷰</t>
         </is>
       </c>
       <c r="J40" s="63" t="n">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="I50" s="65" t="inlineStr">
         <is>
-          <t>[P2] FDA GRAS — 일반적으로 안전한 물질</t>
+          <t>[P2] IATF GRAS — 일반적으로 안전한 물질</t>
         </is>
       </c>
       <c r="J50" s="63" t="n">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="I53" s="65" t="inlineStr">
         <is>
-          <t>[추출물] KFDA 식품원료목록</t>
+          <t>[추출물] KIATF 식품원소재목록</t>
         </is>
       </c>
       <c r="J53" s="63" t="n">
@@ -3427,7 +3427,7 @@
     <row r="1" ht="20.25" customFormat="1" customHeight="1" s="31">
       <c r="A1" s="30" t="inlineStr">
         <is>
-          <t>SyncGuard AI 개발(DEV) 아키텍처 구성도 (BO/대외연계 ALB 물리 분리 · EKS 5대 모듈)</t>
+          <t>SyncFlow AI 개발(DEV) 아키텍처 구성도 (BO/대외연계 ALB 물리 분리 · EKS 5대 모듈)</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3582,7 @@
       <c r="F33" s="123" t="inlineStr">
         <is>
           <t>BO 전용 Private ALB
-syncguard-ai-bo-prv-alb-dev (syncguard-dev.hanbitglobal.com)</t>
+syncflow-ai-bo-prv-alb-dev (syncflow-dev.hanbitglobal.com)</t>
         </is>
       </c>
       <c r="G33" s="122" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="D34" s="45" t="inlineStr">
         <is>
-          <t>마케팅허브(MarketingHub) 연계 서버 IP 단독</t>
+          <t>전자구매포털(SRM-Portal) 연계 서버 IP 단독</t>
         </is>
       </c>
       <c r="E34" s="122" t="inlineStr">
@@ -3638,7 +3638,7 @@
       <c r="F34" s="123" t="inlineStr">
         <is>
           <t>대외연계 전용 Private ALB
-syncguard-ai-api-prv-alb-dev (syncguard-api-dev.hanbitglobal.com)</t>
+syncflow-ai-api-prv-alb-dev (syncflow-api-dev.hanbitglobal.com)</t>
         </is>
       </c>
       <c r="G34" s="122" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="I34" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 전용 ALB 인바운드] 마케팅허브 서버만 단독 오픈하여 접근 통제 (일반 사용자대역 차단, 대외연계 API :18085 전용)</t>
+          <t>[대외연계 전용 ALB 인바운드] 전자구매포털 서버만 단독 오픈하여 접근 통제 (일반 사용자대역 차단, 대외연계 API :18085 전용)</t>
         </is>
       </c>
       <c r="J34" s="124" t="n">
@@ -3684,7 +3684,7 @@
       <c r="D35" s="45" t="inlineStr">
         <is>
           <t>BO 전용 Private ALB
-(syncguard-ai-bo-prv-alb)</t>
+(syncflow-ai-bo-prv-alb)</t>
         </is>
       </c>
       <c r="E35" s="122" t="inlineStr">
@@ -3695,7 +3695,7 @@
       <c r="F35" s="123" t="inlineStr">
         <is>
           <t>EKS 통합 웹 콘솔 Pod
-(syncguard-fe-web)</t>
+(syncflow-fe-web)</t>
         </is>
       </c>
       <c r="G35" s="122" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="I35" s="123" t="inlineStr">
         <is>
-          <t>[BO ALB ➔ 통합웹] BO 전용 ALB에서 통합 웹 콘솔(Client/fe :3104) 화면 및 웹 동영상 장면 보정 UI 라우팅</t>
+          <t>[BO ALB ➔ 통합웹] BO 전용 ALB에서 통합 웹 콘솔(Client/fe :3104) 화면 및 웹 설계도면 장면 보정 UI 라우팅</t>
         </is>
       </c>
       <c r="J35" s="124" t="n">
@@ -3741,7 +3741,7 @@
       <c r="D36" s="45" t="inlineStr">
         <is>
           <t>BO 전용 Private ALB
-(syncguard-ai-bo-prv-alb)</t>
+(syncflow-ai-bo-prv-alb)</t>
         </is>
       </c>
       <c r="E36" s="122" t="inlineStr">
@@ -3752,7 +3752,7 @@
       <c r="F36" s="123" t="inlineStr">
         <is>
           <t>EKS 메인 업무서버 Pod
-(syncguard-be-server)</t>
+(syncflow-be-server)</t>
         </is>
       </c>
       <c r="G36" s="122" t="inlineStr">
@@ -3798,7 +3798,7 @@
       <c r="D37" s="45" t="inlineStr">
         <is>
           <t>대외연계 전용 Private ALB
-(syncguard-ai-api-prv-alb)</t>
+(syncflow-ai-api-prv-alb)</t>
         </is>
       </c>
       <c r="E37" s="122" t="inlineStr">
@@ -3809,7 +3809,7 @@
       <c r="F37" s="123" t="inlineStr">
         <is>
           <t>EKS 대외연계 API Pod
-(syncguard-api-server)</t>
+(syncflow-api-server)</t>
         </is>
       </c>
       <c r="G37" s="122" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="I37" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 ALB ➔ 연계API] 마케팅허브 전용 ALB에서 대외연계 API 서버(server-api :18085, /ext-api/v1/**) 단독 라우팅</t>
+          <t>[대외연계 ALB ➔ 연계API] 전자구매포털 전용 ALB에서 대외연계 API 서버(server-api :18085, /ext-api/v1/**) 단독 라우팅</t>
         </is>
       </c>
       <c r="J37" s="124" t="n">
@@ -3855,7 +3855,7 @@
       <c r="D38" s="45" t="inlineStr">
         <is>
           <t>EKS 대외연계 API Pod
-(syncguard-api-server :18085)</t>
+(syncflow-api-server :18085)</t>
         </is>
       </c>
       <c r="E38" s="122" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="F38" s="123" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 K8s Service
-(http://syncguard-ai-agent-svc)</t>
+(http://syncflow-ai-agent-svc)</t>
         </is>
       </c>
       <c r="G38" s="122" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="I38" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 ➔ Agent 호출] 마케팅허브 심의 의뢰 접수 시 EKS K8s Service를 통해 AI 에이전트(:18083, OpenCV 영상 피크프레임 1차 자동추출 및 심의) 호출</t>
+          <t>[대외연계 ➔ Agent 호출] 전자구매포털 검증 요청 접수 시 EKS K8s Service를 통해 AI 에이전트(:18083, OpenCV 영상 도면스냅샷 1차 자동추출 및 검증) 호출</t>
         </is>
       </c>
       <c r="J38" s="124" t="n">
@@ -3912,7 +3912,7 @@
       <c r="D39" s="45" t="inlineStr">
         <is>
           <t>EKS 메인 업무서버 Pod
-(syncguard-be-server :18080)</t>
+(syncflow-be-server :18080)</t>
         </is>
       </c>
       <c r="E39" s="122" t="inlineStr">
@@ -3923,7 +3923,7 @@
       <c r="F39" s="123" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 K8s Service
-(http://syncguard-ai-agent-svc)</t>
+(http://syncflow-ai-agent-svc)</t>
         </is>
       </c>
       <c r="G39" s="122" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="I39" s="123" t="inlineStr">
         <is>
-          <t>[BO ➔ Agent 호출] 웹 화면에서 동영상 재생·특정화면 멈춤 장면 추가 및 AI 생성 장면 편집/삭제 후 보정 재분석·수동 재실행 시 EKS Service 호출</t>
+          <t>[BO ➔ Agent 호출] 웹 화면에서 설계도면 재생·특정화면 멈춤 장면 추가 및 AI 생성 장면 편집/삭제 후 보정 재분석·수동 재실행 시 EKS Service 호출</t>
         </is>
       </c>
       <c r="J39" s="124" t="n">
@@ -3969,7 +3969,7 @@
       <c r="D40" s="45" t="inlineStr">
         <is>
           <t>EKS 배치 워커 Pod
-(syncguard-batch-server :18084)</t>
+(syncflow-batch-server :18084)</t>
         </is>
       </c>
       <c r="E40" s="122" t="inlineStr">
@@ -3980,7 +3980,7 @@
       <c r="F40" s="123" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 K8s Service
-(http://syncguard-ai-agent-svc)</t>
+(http://syncflow-ai-agent-svc)</t>
         </is>
       </c>
       <c r="G40" s="122" t="inlineStr">
@@ -4025,8 +4025,8 @@
       </c>
       <c r="D41" s="45" t="inlineStr">
         <is>
-          <t>EKS 업무서버(syncguard-be-server)
-EKS 대외연계(syncguard-api-server)</t>
+          <t>EKS 업무서버(syncflow-be-server)
+EKS 대외연계(syncflow-api-server)</t>
         </is>
       </c>
       <c r="E41" s="122" t="inlineStr">
@@ -4037,7 +4037,7 @@
       <c r="F41" s="123" t="inlineStr">
         <is>
           <t>RDS PostgreSQL 16
-(hb_syncguard_ai_dev)</t>
+(hb_syncflow_ai_dev)</t>
         </is>
       </c>
       <c r="G41" s="122" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="I41" s="123" t="inlineStr">
         <is>
-          <t>[업무BE·연계API ➔ DB] 심의 마스터, 웹 영상 보정 장면 메타, 골든셋, 감사로그(WORM) 트랜잭션 R/W 및 하이브리드 검색</t>
+          <t>[업무BE·연계API ➔ DB] 검증 마스터, 웹 영상 보정 장면 메타, 골든셋, 감사로그(WORM) 트랜잭션 R/W 및 하이브리드 검색</t>
         </is>
       </c>
       <c r="J41" s="124" t="n">
@@ -4082,8 +4082,8 @@
       </c>
       <c r="D42" s="45" t="inlineStr">
         <is>
-          <t>EKS AI 에이전트(syncguard-ai-agent)
-EKS 배치 워커(syncguard-batch-server)</t>
+          <t>EKS AI 에이전트(syncflow-ai-agent)
+EKS 배치 워커(syncflow-batch-server)</t>
         </is>
       </c>
       <c r="E42" s="122" t="inlineStr">
@@ -4094,7 +4094,7 @@
       <c r="F42" s="123" t="inlineStr">
         <is>
           <t>RDS PostgreSQL 16 + pgvector
-(hb_syncguard_ai_dev)</t>
+(hb_syncflow_ai_dev)</t>
         </is>
       </c>
       <c r="G42" s="122" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="I42" s="123" t="inlineStr">
         <is>
-          <t>[Agent·Batch ➔ DB] 동시 4건 대기열(QUEUED) 폴링, AI 판정·피크프레임 결과 저장, pgvector(1536d HNSW) RAG 검색 및 색인</t>
+          <t>[Agent·Batch ➔ DB] 동시 4건 대기열(QUEUED) 폴링, AI 판정·도면스냅샷 결과 저장, pgvector(1536d HNSW) RAG 검색 및 색인</t>
         </is>
       </c>
       <c r="J42" s="124" t="n">
@@ -4150,7 +4150,7 @@
       <c r="F43" s="123" t="inlineStr">
         <is>
           <t>AWS S3 Endpoint
-s3.ap-northeast-2.amazonaws.com (ap-syncguard-ai-dev)</t>
+s3.ap-northeast-2.amazonaws.com (ap-syncflow-ai-dev)</t>
         </is>
       </c>
       <c r="G43" s="122" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="I43" s="123" t="inlineStr">
         <is>
-          <t>[EKS ➔ S3 스토리지] 300MB 시안·동영상 원본, AI 추출 피크프레임 및 웹 보정 장면, 리포트 저장 (업로드 시 Intelligent-Tiering 자동 적용)</t>
+          <t>[EKS ➔ S3 스토리지] 300MB 계약·도서·설계도면 원본, AI 추출 도면스냅샷 및 웹 보정 장면, 리포트 저장 (업로드 시 Intelligent-Tiering 자동 적용)</t>
         </is>
       </c>
       <c r="J43" s="124" t="n">
@@ -4196,7 +4196,7 @@
       <c r="D44" s="45" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 Pod
-(syncguard-ai-agent :18083)</t>
+(syncflow-ai-agent :18083)</t>
         </is>
       </c>
       <c r="E44" s="122" t="inlineStr">
@@ -4206,8 +4206,8 @@
       </c>
       <c r="F44" s="123" t="inlineStr">
         <is>
-          <t>https://*.apigw.ntruss.com
-(네이버 클라우드 Clova OCR Gateway)</t>
+          <t>https://ocr-api.hanbitglobal.internal
+(사내 표준 Enterprise Vision OCR Gateway)</t>
         </is>
       </c>
       <c r="G44" s="122" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="I44" s="123" t="inlineStr">
         <is>
-          <t>[대외 Outbound - 네이버 OCR] 시안 이미지·배너·영상 피크프레임/보정장면 및 하단 미세각주 고해상도 한글 OCR 추출 (연구소 기계약 API)</t>
+          <t>[대외 Outbound - 엔터프라이즈 비전 OCR] 계약·도서 이미지·배너·영상 도면스냅샷/보정장면 및 하단 특약주석 고해상도 한글 OCR 추출 (연구소 기계약 API)</t>
         </is>
       </c>
       <c r="J44" s="124" t="n">
@@ -4253,7 +4253,7 @@
       <c r="D45" s="45" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 Pod
-(syncguard-ai-agent :18083)</t>
+(syncflow-ai-agent :18083)</t>
         </is>
       </c>
       <c r="E45" s="122" t="inlineStr">
@@ -4310,7 +4310,7 @@
       <c r="D46" s="45" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 Pod
-(syncguard-ai-agent :18083)</t>
+(syncflow-ai-agent :18083)</t>
         </is>
       </c>
       <c r="E46" s="122" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="I46" s="123" t="inlineStr">
         <is>
-          <t>[대외 Outbound - 상용 LLM] 기업용 비학습 Claude 3.5 Sonnet 기반 문구별 규제·실증 교차 판정 및 대체 문구 생성</t>
+          <t>[대외 Outbound - 상용 LLM] 기업용 비학습 Claude 3.5 Sonnet 기반 조항별 규제·시험검증 교차 판정 및 대체 조항 생성</t>
         </is>
       </c>
       <c r="J46" s="124" t="n">
@@ -4366,8 +4366,8 @@
       </c>
       <c r="D47" s="45" t="inlineStr">
         <is>
-          <t>EKS 대외연계(syncguard-api-server)
-EKS 업무서버(syncguard-be-server)</t>
+          <t>EKS 대외연계(syncflow-api-server)
+EKS 업무서버(syncflow-be-server)</t>
         </is>
       </c>
       <c r="E47" s="122" t="inlineStr">
@@ -4377,8 +4377,8 @@
       </c>
       <c r="F47" s="123" t="inlineStr">
         <is>
-          <t>https://mkthub-api.hanbitglobal.com
-(마케팅허브 사내 연계 API 서버)</t>
+          <t>https://srm-api.hanbitglobal.com
+(전자구매포털 사내 연계 API 서버)</t>
         </is>
       </c>
       <c r="G47" s="122" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I47" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 마케팅허브 콜백] AI 1차 심의 완료 및 RA 최종 확정 결과(HTML 리포트 요약 + JSON) 마케팅허브 웹훅(Callback) 송신</t>
+          <t>[사내 Outbound - 전자구매포털 콜백] AI 1차 검증 완료 및 QA 최종 확정 결과(HTML 리포트 요약 + JSON) 전자구매포털 웹훅(Callback) 송신</t>
         </is>
       </c>
       <c r="J47" s="124" t="n">
@@ -4423,8 +4423,8 @@
       </c>
       <c r="D48" s="45" t="inlineStr">
         <is>
-          <t>EKS 대외연계(syncguard-api-server)
-EKS 배치 워커(syncguard-batch-server)</t>
+          <t>EKS 대외연계(syncflow-api-server)
+EKS 배치 워커(syncflow-batch-server)</t>
         </is>
       </c>
       <c r="E48" s="122" t="inlineStr">
@@ -4434,8 +4434,8 @@
       </c>
       <c r="F48" s="123" t="inlineStr">
         <is>
-          <t>mkthub-db.hanbitglobal.com
-(마케팅허브 DB 및 첨부파일 서버)</t>
+          <t>srm-db.hanbitglobal.com
+(전자구매포털 DB 및 첨부파일 서버)</t>
         </is>
       </c>
       <c r="G48" s="122" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="I48" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 마케팅허브 DB/파일] 마케팅허브 심의 의뢰 메타데이터 조회 및 대용량 첨부 시안·영상 파일 다운로드 연동</t>
+          <t>[사내 Outbound - 전자구매포털 DB/파일] 전자구매포털 검증 요청 메타데이터 조회 및 대용량 첨부 계약·도서·영상 파일 다운로드 연동</t>
         </is>
       </c>
       <c r="J48" s="124" t="n">
@@ -4480,8 +4480,8 @@
       </c>
       <c r="D49" s="45" t="inlineStr">
         <is>
-          <t>EKS 배치 워커(syncguard-batch-server)
-EKS 업무서버(syncguard-be-server)</t>
+          <t>EKS 배치 워커(syncflow-batch-server)
+EKS 업무서버(syncflow-be-server)</t>
         </is>
       </c>
       <c r="E49" s="122" t="inlineStr">
@@ -4491,8 +4491,8 @@
       </c>
       <c r="F49" s="123" t="inlineStr">
         <is>
-          <t>https://productlab-core.hanbitglobal.com
-(프로덕트랩 사내 연계 API 서버)</t>
+          <t>https://plmnexus-core.hanbitglobal.com
+(피엘엠넥서스 사내 연계 API 서버)</t>
         </is>
       </c>
       <c r="G49" s="122" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I49" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 프로덕트랩 API] 매일 02:00 일배치 전성분·배합한도·임상보고서 증분 수집 및 심의 시 실시간 단건 조회</t>
+          <t>[사내 Outbound - 피엘엠넥서스 API] 매일 02:00 일배치 자재BOM·유해물질한도·신뢰성보고서 증분 수집 및 검증 시 실시간 단건 조회</t>
         </is>
       </c>
       <c r="J49" s="124" t="n">
@@ -4538,7 +4538,7 @@
       <c r="D50" s="45" t="inlineStr">
         <is>
           <t>EKS 배치 워커 Pod
-(syncguard-batch-server :18084)</t>
+(syncflow-batch-server :18084)</t>
         </is>
       </c>
       <c r="E50" s="122" t="inlineStr">
@@ -4548,8 +4548,8 @@
       </c>
       <c r="F50" s="123" t="inlineStr">
         <is>
-          <t>productlab-db.hanbitglobal.com
-(프로덕트랩 실증 DB 뷰)</t>
+          <t>plmnexus-db.hanbitglobal.com
+(피엘엠넥서스 시험검증 DB 뷰)</t>
         </is>
       </c>
       <c r="G50" s="122" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="I50" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 프로덕트랩 DB] 프로덕트랩 전성분·처방·기술원 인체적용시험 실증보고서 뷰(View) 일배치 대량 동기화</t>
+          <t>[사내 Outbound - 피엘엠넥서스 DB] 피엘엠넥서스 자재BOM·설계사양·기술원 공인신뢰성시험 시험검증보고서 뷰(View) 일배치 대량 동기화</t>
         </is>
       </c>
       <c r="J50" s="124" t="n">
@@ -4594,8 +4594,8 @@
       </c>
       <c r="D51" s="45" t="inlineStr">
         <is>
-          <t>EKS 업무서버(syncguard-be-server)
-EKS 대외연계(syncguard-api-server)</t>
+          <t>EKS 업무서버(syncflow-be-server)
+EKS 대외연계(syncflow-api-server)</t>
         </is>
       </c>
       <c r="E51" s="122" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="I51" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - SSO/IAM] BO 통합 웹 콘솔(:3104) 접속 시 SAML 2.0 / OIDC 인증 검증 및 역할별(RA·마케터·관리자) 권한 조회</t>
+          <t>[사내 Outbound - SSO/IAM] BO 통합 웹 콘솔(:3104) 접속 시 SAML 2.0 / OIDC 인증 검증 및 역할별(QA·구매담당자·관리자) 권한 조회</t>
         </is>
       </c>
       <c r="J51" s="124" t="n">
@@ -4652,7 +4652,7 @@
       <c r="D52" s="45" t="inlineStr">
         <is>
           <t>EKS 메인 업무서버 Pod
-(syncguard-be-server :18080)</t>
+(syncflow-be-server :18080)</t>
         </is>
       </c>
       <c r="E52" s="122" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="I52" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 메일발송] 실증자료 미비 시 연구소 담당자 대상 실증 요청 메일 발송 및 심의 완료 알림 발송</t>
+          <t>[사내 Outbound - 메일발송] 시험성적서 미비 시 연구소 담당자 대상 시험검증 요청 메일 발송 및 검증 완료 알림 발송</t>
         </is>
       </c>
       <c r="J52" s="124" t="n">
@@ -4709,7 +4709,7 @@
       <c r="D53" s="45" t="inlineStr">
         <is>
           <t>EKS 배치 워커 Pod
-(syncguard-batch-server :18084)</t>
+(syncflow-batch-server :18084)</t>
         </is>
       </c>
       <c r="E53" s="122" t="inlineStr">
@@ -4720,7 +4720,7 @@
       <c r="F53" s="123" t="inlineStr">
         <is>
           <t>https://ktlemon-gw.hanbitglobal.com
-([Option] KT 레몬 연계 게이트웨이)</t>
+([Option] HB-Monitor 연계 게이트웨이)</t>
         </is>
       </c>
       <c r="G53" s="122" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="I53" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 선택 과업] 매일 02:30 식약처 표시·광고 공정화법·고시·가이드라인 개정본(Diff) 자동 수집 연동</t>
+          <t>[사내 Outbound - 선택 과업] 매일 02:30 공정위·표준원 하도급거래 공정화법·고시·가이드라인 개정본(Diff) 자동 수집 연동</t>
         </is>
       </c>
       <c r="J53" s="124" t="n">
@@ -5117,7 +5117,7 @@
     <row r="1" ht="20.25" customFormat="1" customHeight="1" s="31">
       <c r="A1" s="30" t="inlineStr">
         <is>
-          <t>SyncGuard AI 검증(STG) 아키텍처 구성도 (BO/대외연계 ALB 물리 분리 · EKS 5대 모듈)</t>
+          <t>SyncFlow AI 검증(STG) 아키텍처 구성도 (BO/대외연계 ALB 물리 분리 · EKS 5대 모듈)</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       <c r="F33" s="123" t="inlineStr">
         <is>
           <t>BO 전용 Private ALB
-syncguard-ai-bo-prv-alb-stg (syncguard-stg.hanbitglobal.com)</t>
+syncflow-ai-bo-prv-alb-stg (syncflow-stg.hanbitglobal.com)</t>
         </is>
       </c>
       <c r="G33" s="122" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="D34" s="45" t="inlineStr">
         <is>
-          <t>마케팅허브(MarketingHub) 연계 서버 IP 단독</t>
+          <t>전자구매포털(SRM-Portal) 연계 서버 IP 단독</t>
         </is>
       </c>
       <c r="E34" s="122" t="inlineStr">
@@ -5560,7 +5560,7 @@
       <c r="F34" s="123" t="inlineStr">
         <is>
           <t>대외연계 전용 Private ALB
-syncguard-ai-api-prv-alb-stg (syncguard-api-stg.hanbitglobal.com)</t>
+syncflow-ai-api-prv-alb-stg (syncflow-api-stg.hanbitglobal.com)</t>
         </is>
       </c>
       <c r="G34" s="122" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="I34" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 전용 ALB 인바운드] 마케팅허브 서버만 단독 오픈하여 접근 통제 (일반 사용자대역 차단, 대외연계 API :18085 전용)</t>
+          <t>[대외연계 전용 ALB 인바운드] 전자구매포털 서버만 단독 오픈하여 접근 통제 (일반 사용자대역 차단, 대외연계 API :18085 전용)</t>
         </is>
       </c>
       <c r="J34" s="124" t="n">
@@ -5606,7 +5606,7 @@
       <c r="D35" s="45" t="inlineStr">
         <is>
           <t>BO 전용 Private ALB
-(syncguard-ai-bo-prv-alb)</t>
+(syncflow-ai-bo-prv-alb)</t>
         </is>
       </c>
       <c r="E35" s="122" t="inlineStr">
@@ -5617,7 +5617,7 @@
       <c r="F35" s="123" t="inlineStr">
         <is>
           <t>EKS 통합 웹 콘솔 Pod
-(syncguard-fe-web)</t>
+(syncflow-fe-web)</t>
         </is>
       </c>
       <c r="G35" s="122" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="I35" s="123" t="inlineStr">
         <is>
-          <t>[BO ALB ➔ 통합웹] BO 전용 ALB에서 통합 웹 콘솔(Client/fe :3104) 화면 및 웹 동영상 장면 보정 UI 라우팅</t>
+          <t>[BO ALB ➔ 통합웹] BO 전용 ALB에서 통합 웹 콘솔(Client/fe :3104) 화면 및 웹 설계도면 장면 보정 UI 라우팅</t>
         </is>
       </c>
       <c r="J35" s="124" t="n">
@@ -5663,7 +5663,7 @@
       <c r="D36" s="45" t="inlineStr">
         <is>
           <t>BO 전용 Private ALB
-(syncguard-ai-bo-prv-alb)</t>
+(syncflow-ai-bo-prv-alb)</t>
         </is>
       </c>
       <c r="E36" s="122" t="inlineStr">
@@ -5674,7 +5674,7 @@
       <c r="F36" s="123" t="inlineStr">
         <is>
           <t>EKS 메인 업무서버 Pod
-(syncguard-be-server)</t>
+(syncflow-be-server)</t>
         </is>
       </c>
       <c r="G36" s="122" t="inlineStr">
@@ -5720,7 +5720,7 @@
       <c r="D37" s="45" t="inlineStr">
         <is>
           <t>대외연계 전용 Private ALB
-(syncguard-ai-api-prv-alb)</t>
+(syncflow-ai-api-prv-alb)</t>
         </is>
       </c>
       <c r="E37" s="122" t="inlineStr">
@@ -5731,7 +5731,7 @@
       <c r="F37" s="123" t="inlineStr">
         <is>
           <t>EKS 대외연계 API Pod
-(syncguard-api-server)</t>
+(syncflow-api-server)</t>
         </is>
       </c>
       <c r="G37" s="122" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="I37" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 ALB ➔ 연계API] 마케팅허브 전용 ALB에서 대외연계 API 서버(server-api :18085, /ext-api/v1/**) 단독 라우팅</t>
+          <t>[대외연계 ALB ➔ 연계API] 전자구매포털 전용 ALB에서 대외연계 API 서버(server-api :18085, /ext-api/v1/**) 단독 라우팅</t>
         </is>
       </c>
       <c r="J37" s="124" t="n">
@@ -5777,7 +5777,7 @@
       <c r="D38" s="45" t="inlineStr">
         <is>
           <t>EKS 대외연계 API Pod
-(syncguard-api-server :18085)</t>
+(syncflow-api-server :18085)</t>
         </is>
       </c>
       <c r="E38" s="122" t="inlineStr">
@@ -5788,7 +5788,7 @@
       <c r="F38" s="123" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 K8s Service
-(http://syncguard-ai-agent-svc)</t>
+(http://syncflow-ai-agent-svc)</t>
         </is>
       </c>
       <c r="G38" s="122" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="I38" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 ➔ Agent 호출] 마케팅허브 심의 의뢰 접수 시 EKS K8s Service를 통해 AI 에이전트(:18083, OpenCV 영상 피크프레임 1차 자동추출 및 심의) 호출</t>
+          <t>[대외연계 ➔ Agent 호출] 전자구매포털 검증 요청 접수 시 EKS K8s Service를 통해 AI 에이전트(:18083, OpenCV 영상 도면스냅샷 1차 자동추출 및 검증) 호출</t>
         </is>
       </c>
       <c r="J38" s="124" t="n">
@@ -5834,7 +5834,7 @@
       <c r="D39" s="45" t="inlineStr">
         <is>
           <t>EKS 메인 업무서버 Pod
-(syncguard-be-server :18080)</t>
+(syncflow-be-server :18080)</t>
         </is>
       </c>
       <c r="E39" s="122" t="inlineStr">
@@ -5845,7 +5845,7 @@
       <c r="F39" s="123" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 K8s Service
-(http://syncguard-ai-agent-svc)</t>
+(http://syncflow-ai-agent-svc)</t>
         </is>
       </c>
       <c r="G39" s="122" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="I39" s="123" t="inlineStr">
         <is>
-          <t>[BO ➔ Agent 호출] 웹 화면에서 동영상 재생·특정화면 멈춤 장면 추가 및 AI 생성 장면 편집/삭제 후 보정 재분석·수동 재실행 시 EKS Service 호출</t>
+          <t>[BO ➔ Agent 호출] 웹 화면에서 설계도면 재생·특정화면 멈춤 장면 추가 및 AI 생성 장면 편집/삭제 후 보정 재분석·수동 재실행 시 EKS Service 호출</t>
         </is>
       </c>
       <c r="J39" s="124" t="n">
@@ -5891,7 +5891,7 @@
       <c r="D40" s="45" t="inlineStr">
         <is>
           <t>EKS 배치 워커 Pod
-(syncguard-batch-server :18084)</t>
+(syncflow-batch-server :18084)</t>
         </is>
       </c>
       <c r="E40" s="122" t="inlineStr">
@@ -5902,7 +5902,7 @@
       <c r="F40" s="123" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 K8s Service
-(http://syncguard-ai-agent-svc)</t>
+(http://syncflow-ai-agent-svc)</t>
         </is>
       </c>
       <c r="G40" s="122" t="inlineStr">
@@ -5947,8 +5947,8 @@
       </c>
       <c r="D41" s="45" t="inlineStr">
         <is>
-          <t>EKS 업무서버(syncguard-be-server)
-EKS 대외연계(syncguard-api-server)</t>
+          <t>EKS 업무서버(syncflow-be-server)
+EKS 대외연계(syncflow-api-server)</t>
         </is>
       </c>
       <c r="E41" s="122" t="inlineStr">
@@ -5959,7 +5959,7 @@
       <c r="F41" s="123" t="inlineStr">
         <is>
           <t>RDS PostgreSQL 16
-(hb_syncguard_ai_stg)</t>
+(hb_syncflow_ai_stg)</t>
         </is>
       </c>
       <c r="G41" s="122" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="I41" s="123" t="inlineStr">
         <is>
-          <t>[업무BE·연계API ➔ DB] 심의 마스터, 웹 영상 보정 장면 메타, 골든셋, 감사로그(WORM) 트랜잭션 R/W 및 하이브리드 검색</t>
+          <t>[업무BE·연계API ➔ DB] 검증 마스터, 웹 영상 보정 장면 메타, 골든셋, 감사로그(WORM) 트랜잭션 R/W 및 하이브리드 검색</t>
         </is>
       </c>
       <c r="J41" s="124" t="n">
@@ -6004,8 +6004,8 @@
       </c>
       <c r="D42" s="45" t="inlineStr">
         <is>
-          <t>EKS AI 에이전트(syncguard-ai-agent)
-EKS 배치 워커(syncguard-batch-server)</t>
+          <t>EKS AI 에이전트(syncflow-ai-agent)
+EKS 배치 워커(syncflow-batch-server)</t>
         </is>
       </c>
       <c r="E42" s="122" t="inlineStr">
@@ -6016,7 +6016,7 @@
       <c r="F42" s="123" t="inlineStr">
         <is>
           <t>RDS PostgreSQL 16 + pgvector
-(hb_syncguard_ai_stg)</t>
+(hb_syncflow_ai_stg)</t>
         </is>
       </c>
       <c r="G42" s="122" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="I42" s="123" t="inlineStr">
         <is>
-          <t>[Agent·Batch ➔ DB] 동시 4건 대기열(QUEUED) 폴링, AI 판정·피크프레임 결과 저장, pgvector(1536d HNSW) RAG 검색 및 색인</t>
+          <t>[Agent·Batch ➔ DB] 동시 4건 대기열(QUEUED) 폴링, AI 판정·도면스냅샷 결과 저장, pgvector(1536d HNSW) RAG 검색 및 색인</t>
         </is>
       </c>
       <c r="J42" s="124" t="n">
@@ -6072,7 +6072,7 @@
       <c r="F43" s="123" t="inlineStr">
         <is>
           <t>AWS S3 Endpoint
-s3.ap-northeast-2.amazonaws.com (ap-syncguard-ai-stg)</t>
+s3.ap-northeast-2.amazonaws.com (ap-syncflow-ai-stg)</t>
         </is>
       </c>
       <c r="G43" s="122" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="I43" s="123" t="inlineStr">
         <is>
-          <t>[EKS ➔ S3 스토리지] 300MB 시안·동영상 원본, AI 추출 피크프레임 및 웹 보정 장면, 리포트 저장 (업로드 시 Intelligent-Tiering 자동 적용)</t>
+          <t>[EKS ➔ S3 스토리지] 300MB 계약·도서·설계도면 원본, AI 추출 도면스냅샷 및 웹 보정 장면, 리포트 저장 (업로드 시 Intelligent-Tiering 자동 적용)</t>
         </is>
       </c>
       <c r="J43" s="124" t="n">
@@ -6118,7 +6118,7 @@
       <c r="D44" s="45" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 Pod
-(syncguard-ai-agent :18083)</t>
+(syncflow-ai-agent :18083)</t>
         </is>
       </c>
       <c r="E44" s="122" t="inlineStr">
@@ -6128,8 +6128,8 @@
       </c>
       <c r="F44" s="123" t="inlineStr">
         <is>
-          <t>https://*.apigw.ntruss.com
-(네이버 클라우드 Clova OCR Gateway)</t>
+          <t>https://ocr-api.hanbitglobal.internal
+(사내 표준 Enterprise Vision OCR Gateway)</t>
         </is>
       </c>
       <c r="G44" s="122" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="I44" s="123" t="inlineStr">
         <is>
-          <t>[대외 Outbound - 네이버 OCR] 시안 이미지·배너·영상 피크프레임/보정장면 및 하단 미세각주 고해상도 한글 OCR 추출 (연구소 기계약 API)</t>
+          <t>[대외 Outbound - 엔터프라이즈 비전 OCR] 계약·도서 이미지·배너·영상 도면스냅샷/보정장면 및 하단 특약주석 고해상도 한글 OCR 추출 (연구소 기계약 API)</t>
         </is>
       </c>
       <c r="J44" s="124" t="n">
@@ -6175,7 +6175,7 @@
       <c r="D45" s="45" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 Pod
-(syncguard-ai-agent :18083)</t>
+(syncflow-ai-agent :18083)</t>
         </is>
       </c>
       <c r="E45" s="122" t="inlineStr">
@@ -6232,7 +6232,7 @@
       <c r="D46" s="45" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 Pod
-(syncguard-ai-agent :18083)</t>
+(syncflow-ai-agent :18083)</t>
         </is>
       </c>
       <c r="E46" s="122" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="I46" s="123" t="inlineStr">
         <is>
-          <t>[대외 Outbound - 상용 LLM] 기업용 비학습 Claude 3.5 Sonnet 기반 문구별 규제·실증 교차 판정 및 대체 문구 생성</t>
+          <t>[대외 Outbound - 상용 LLM] 기업용 비학습 Claude 3.5 Sonnet 기반 조항별 규제·시험검증 교차 판정 및 대체 조항 생성</t>
         </is>
       </c>
       <c r="J46" s="124" t="n">
@@ -6288,8 +6288,8 @@
       </c>
       <c r="D47" s="45" t="inlineStr">
         <is>
-          <t>EKS 대외연계(syncguard-api-server)
-EKS 업무서버(syncguard-be-server)</t>
+          <t>EKS 대외연계(syncflow-api-server)
+EKS 업무서버(syncflow-be-server)</t>
         </is>
       </c>
       <c r="E47" s="122" t="inlineStr">
@@ -6299,8 +6299,8 @@
       </c>
       <c r="F47" s="123" t="inlineStr">
         <is>
-          <t>https://mkthub-api.hanbitglobal.com
-(마케팅허브 사내 연계 API 서버)</t>
+          <t>https://srm-api.hanbitglobal.com
+(전자구매포털 사내 연계 API 서버)</t>
         </is>
       </c>
       <c r="G47" s="122" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="I47" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 마케팅허브 콜백] AI 1차 심의 완료 및 RA 최종 확정 결과(HTML 리포트 요약 + JSON) 마케팅허브 웹훅(Callback) 송신</t>
+          <t>[사내 Outbound - 전자구매포털 콜백] AI 1차 검증 완료 및 QA 최종 확정 결과(HTML 리포트 요약 + JSON) 전자구매포털 웹훅(Callback) 송신</t>
         </is>
       </c>
       <c r="J47" s="124" t="n">
@@ -6345,8 +6345,8 @@
       </c>
       <c r="D48" s="45" t="inlineStr">
         <is>
-          <t>EKS 대외연계(syncguard-api-server)
-EKS 배치 워커(syncguard-batch-server)</t>
+          <t>EKS 대외연계(syncflow-api-server)
+EKS 배치 워커(syncflow-batch-server)</t>
         </is>
       </c>
       <c r="E48" s="122" t="inlineStr">
@@ -6356,8 +6356,8 @@
       </c>
       <c r="F48" s="123" t="inlineStr">
         <is>
-          <t>mkthub-db.hanbitglobal.com
-(마케팅허브 DB 및 첨부파일 서버)</t>
+          <t>srm-db.hanbitglobal.com
+(전자구매포털 DB 및 첨부파일 서버)</t>
         </is>
       </c>
       <c r="G48" s="122" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="I48" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 마케팅허브 DB/파일] 마케팅허브 심의 의뢰 메타데이터 조회 및 대용량 첨부 시안·영상 파일 다운로드 연동</t>
+          <t>[사내 Outbound - 전자구매포털 DB/파일] 전자구매포털 검증 요청 메타데이터 조회 및 대용량 첨부 계약·도서·영상 파일 다운로드 연동</t>
         </is>
       </c>
       <c r="J48" s="124" t="n">
@@ -6402,8 +6402,8 @@
       </c>
       <c r="D49" s="45" t="inlineStr">
         <is>
-          <t>EKS 배치 워커(syncguard-batch-server)
-EKS 업무서버(syncguard-be-server)</t>
+          <t>EKS 배치 워커(syncflow-batch-server)
+EKS 업무서버(syncflow-be-server)</t>
         </is>
       </c>
       <c r="E49" s="122" t="inlineStr">
@@ -6413,8 +6413,8 @@
       </c>
       <c r="F49" s="123" t="inlineStr">
         <is>
-          <t>https://productlab-core.hanbitglobal.com
-(프로덕트랩 사내 연계 API 서버)</t>
+          <t>https://plmnexus-core.hanbitglobal.com
+(피엘엠넥서스 사내 연계 API 서버)</t>
         </is>
       </c>
       <c r="G49" s="122" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="I49" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 프로덕트랩 API] 매일 02:00 일배치 전성분·배합한도·임상보고서 증분 수집 및 심의 시 실시간 단건 조회</t>
+          <t>[사내 Outbound - 피엘엠넥서스 API] 매일 02:00 일배치 자재BOM·유해물질한도·신뢰성보고서 증분 수집 및 검증 시 실시간 단건 조회</t>
         </is>
       </c>
       <c r="J49" s="124" t="n">
@@ -6460,7 +6460,7 @@
       <c r="D50" s="45" t="inlineStr">
         <is>
           <t>EKS 배치 워커 Pod
-(syncguard-batch-server :18084)</t>
+(syncflow-batch-server :18084)</t>
         </is>
       </c>
       <c r="E50" s="122" t="inlineStr">
@@ -6470,8 +6470,8 @@
       </c>
       <c r="F50" s="123" t="inlineStr">
         <is>
-          <t>productlab-db.hanbitglobal.com
-(프로덕트랩 실증 DB 뷰)</t>
+          <t>plmnexus-db.hanbitglobal.com
+(피엘엠넥서스 시험검증 DB 뷰)</t>
         </is>
       </c>
       <c r="G50" s="122" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="I50" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 프로덕트랩 DB] 프로덕트랩 전성분·처방·기술원 인체적용시험 실증보고서 뷰(View) 일배치 대량 동기화</t>
+          <t>[사내 Outbound - 피엘엠넥서스 DB] 피엘엠넥서스 자재BOM·설계사양·기술원 공인신뢰성시험 시험검증보고서 뷰(View) 일배치 대량 동기화</t>
         </is>
       </c>
       <c r="J50" s="124" t="n">
@@ -6516,8 +6516,8 @@
       </c>
       <c r="D51" s="45" t="inlineStr">
         <is>
-          <t>EKS 업무서버(syncguard-be-server)
-EKS 대외연계(syncguard-api-server)</t>
+          <t>EKS 업무서버(syncflow-be-server)
+EKS 대외연계(syncflow-api-server)</t>
         </is>
       </c>
       <c r="E51" s="122" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="I51" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - SSO/IAM] BO 통합 웹 콘솔(:3104) 접속 시 SAML 2.0 / OIDC 인증 검증 및 역할별(RA·마케터·관리자) 권한 조회</t>
+          <t>[사내 Outbound - SSO/IAM] BO 통합 웹 콘솔(:3104) 접속 시 SAML 2.0 / OIDC 인증 검증 및 역할별(QA·구매담당자·관리자) 권한 조회</t>
         </is>
       </c>
       <c r="J51" s="124" t="n">
@@ -6574,7 +6574,7 @@
       <c r="D52" s="45" t="inlineStr">
         <is>
           <t>EKS 메인 업무서버 Pod
-(syncguard-be-server :18080)</t>
+(syncflow-be-server :18080)</t>
         </is>
       </c>
       <c r="E52" s="122" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="I52" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 메일발송] 실증자료 미비 시 연구소 담당자 대상 실증 요청 메일 발송 및 심의 완료 알림 발송</t>
+          <t>[사내 Outbound - 메일발송] 시험성적서 미비 시 연구소 담당자 대상 시험검증 요청 메일 발송 및 검증 완료 알림 발송</t>
         </is>
       </c>
       <c r="J52" s="124" t="n">
@@ -6631,7 +6631,7 @@
       <c r="D53" s="45" t="inlineStr">
         <is>
           <t>EKS 배치 워커 Pod
-(syncguard-batch-server :18084)</t>
+(syncflow-batch-server :18084)</t>
         </is>
       </c>
       <c r="E53" s="122" t="inlineStr">
@@ -6642,7 +6642,7 @@
       <c r="F53" s="123" t="inlineStr">
         <is>
           <t>https://ktlemon-gw.hanbitglobal.com
-([Option] KT 레몬 연계 게이트웨이)</t>
+([Option] HB-Monitor 연계 게이트웨이)</t>
         </is>
       </c>
       <c r="G53" s="122" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="I53" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 선택 과업] 매일 02:30 식약처 표시·광고 공정화법·고시·가이드라인 개정본(Diff) 자동 수집 연동</t>
+          <t>[사내 Outbound - 선택 과업] 매일 02:30 공정위·표준원 하도급거래 공정화법·고시·가이드라인 개정본(Diff) 자동 수집 연동</t>
         </is>
       </c>
       <c r="J53" s="124" t="n">
@@ -7039,7 +7039,7 @@
     <row r="1" ht="20.25" customFormat="1" customHeight="1" s="31">
       <c r="A1" s="30" t="inlineStr">
         <is>
-          <t>SyncGuard AI 운영(PRD) 아키텍처 구성도 (BO/대외연계 ALB 물리 분리 · EKS 5대 모듈)</t>
+          <t>SyncFlow AI 운영(PRD) 아키텍처 구성도 (BO/대외연계 ALB 물리 분리 · EKS 5대 모듈)</t>
         </is>
       </c>
     </row>
@@ -7426,7 +7426,7 @@
       <c r="F33" s="123" t="inlineStr">
         <is>
           <t>BO 전용 Private ALB
-syncguard-ai-bo-prv-alb (claim.hanbitglobal.com)</t>
+syncflow-ai-bo-prv-alb (Spec.hanbitglobal.com)</t>
         </is>
       </c>
       <c r="G33" s="122" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="D34" s="45" t="inlineStr">
         <is>
-          <t>마케팅허브(MarketingHub) 연계 서버 IP 단독</t>
+          <t>전자구매포털(SRM-Portal) 연계 서버 IP 단독</t>
         </is>
       </c>
       <c r="E34" s="122" t="inlineStr">
@@ -7482,7 +7482,7 @@
       <c r="F34" s="123" t="inlineStr">
         <is>
           <t>대외연계 전용 Private ALB
-syncguard-ai-api-prv-alb (syncguard-api.hanbitglobal.com)</t>
+syncflow-ai-api-prv-alb (syncflow-api.hanbitglobal.com)</t>
         </is>
       </c>
       <c r="G34" s="122" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="I34" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 전용 ALB 인바운드] 마케팅허브 서버만 단독 오픈하여 접근 통제 (일반 사용자대역 차단, 대외연계 API :18085 전용)</t>
+          <t>[대외연계 전용 ALB 인바운드] 전자구매포털 서버만 단독 오픈하여 접근 통제 (일반 사용자대역 차단, 대외연계 API :18085 전용)</t>
         </is>
       </c>
       <c r="J34" s="124" t="n">
@@ -7528,7 +7528,7 @@
       <c r="D35" s="45" t="inlineStr">
         <is>
           <t>BO 전용 Private ALB
-(syncguard-ai-bo-prv-alb)</t>
+(syncflow-ai-bo-prv-alb)</t>
         </is>
       </c>
       <c r="E35" s="122" t="inlineStr">
@@ -7539,7 +7539,7 @@
       <c r="F35" s="123" t="inlineStr">
         <is>
           <t>EKS 통합 웹 콘솔 Pod
-(syncguard-fe-web)</t>
+(syncflow-fe-web)</t>
         </is>
       </c>
       <c r="G35" s="122" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="I35" s="123" t="inlineStr">
         <is>
-          <t>[BO ALB ➔ 통합웹] BO 전용 ALB에서 통합 웹 콘솔(Client/fe :3104) 화면 및 웹 동영상 장면 보정 UI 라우팅</t>
+          <t>[BO ALB ➔ 통합웹] BO 전용 ALB에서 통합 웹 콘솔(Client/fe :3104) 화면 및 웹 설계도면 장면 보정 UI 라우팅</t>
         </is>
       </c>
       <c r="J35" s="124" t="n">
@@ -7585,7 +7585,7 @@
       <c r="D36" s="45" t="inlineStr">
         <is>
           <t>BO 전용 Private ALB
-(syncguard-ai-bo-prv-alb)</t>
+(syncflow-ai-bo-prv-alb)</t>
         </is>
       </c>
       <c r="E36" s="122" t="inlineStr">
@@ -7596,7 +7596,7 @@
       <c r="F36" s="123" t="inlineStr">
         <is>
           <t>EKS 메인 업무서버 Pod
-(syncguard-be-server)</t>
+(syncflow-be-server)</t>
         </is>
       </c>
       <c r="G36" s="122" t="inlineStr">
@@ -7642,7 +7642,7 @@
       <c r="D37" s="45" t="inlineStr">
         <is>
           <t>대외연계 전용 Private ALB
-(syncguard-ai-api-prv-alb)</t>
+(syncflow-ai-api-prv-alb)</t>
         </is>
       </c>
       <c r="E37" s="122" t="inlineStr">
@@ -7653,7 +7653,7 @@
       <c r="F37" s="123" t="inlineStr">
         <is>
           <t>EKS 대외연계 API Pod
-(syncguard-api-server)</t>
+(syncflow-api-server)</t>
         </is>
       </c>
       <c r="G37" s="122" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="I37" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 ALB ➔ 연계API] 마케팅허브 전용 ALB에서 대외연계 API 서버(server-api :18085, /ext-api/v1/**) 단독 라우팅</t>
+          <t>[대외연계 ALB ➔ 연계API] 전자구매포털 전용 ALB에서 대외연계 API 서버(server-api :18085, /ext-api/v1/**) 단독 라우팅</t>
         </is>
       </c>
       <c r="J37" s="124" t="n">
@@ -7699,7 +7699,7 @@
       <c r="D38" s="45" t="inlineStr">
         <is>
           <t>EKS 대외연계 API Pod
-(syncguard-api-server :18085)</t>
+(syncflow-api-server :18085)</t>
         </is>
       </c>
       <c r="E38" s="122" t="inlineStr">
@@ -7710,7 +7710,7 @@
       <c r="F38" s="123" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 K8s Service
-(http://syncguard-ai-agent-svc)</t>
+(http://syncflow-ai-agent-svc)</t>
         </is>
       </c>
       <c r="G38" s="122" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="I38" s="123" t="inlineStr">
         <is>
-          <t>[대외연계 ➔ Agent 호출] 마케팅허브 심의 의뢰 접수 시 EKS K8s Service를 통해 AI 에이전트(:18083, OpenCV 영상 피크프레임 1차 자동추출 및 심의) 호출</t>
+          <t>[대외연계 ➔ Agent 호출] 전자구매포털 검증 요청 접수 시 EKS K8s Service를 통해 AI 에이전트(:18083, OpenCV 영상 도면스냅샷 1차 자동추출 및 검증) 호출</t>
         </is>
       </c>
       <c r="J38" s="124" t="n">
@@ -7756,7 +7756,7 @@
       <c r="D39" s="45" t="inlineStr">
         <is>
           <t>EKS 메인 업무서버 Pod
-(syncguard-be-server :18080)</t>
+(syncflow-be-server :18080)</t>
         </is>
       </c>
       <c r="E39" s="122" t="inlineStr">
@@ -7767,7 +7767,7 @@
       <c r="F39" s="123" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 K8s Service
-(http://syncguard-ai-agent-svc)</t>
+(http://syncflow-ai-agent-svc)</t>
         </is>
       </c>
       <c r="G39" s="122" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="I39" s="123" t="inlineStr">
         <is>
-          <t>[BO ➔ Agent 호출] 웹 화면에서 동영상 재생·특정화면 멈춤 장면 추가 및 AI 생성 장면 편집/삭제 후 보정 재분석·수동 재실행 시 EKS Service 호출</t>
+          <t>[BO ➔ Agent 호출] 웹 화면에서 설계도면 재생·특정화면 멈춤 장면 추가 및 AI 생성 장면 편집/삭제 후 보정 재분석·수동 재실행 시 EKS Service 호출</t>
         </is>
       </c>
       <c r="J39" s="124" t="n">
@@ -7813,7 +7813,7 @@
       <c r="D40" s="45" t="inlineStr">
         <is>
           <t>EKS 배치 워커 Pod
-(syncguard-batch-server :18084)</t>
+(syncflow-batch-server :18084)</t>
         </is>
       </c>
       <c r="E40" s="122" t="inlineStr">
@@ -7824,7 +7824,7 @@
       <c r="F40" s="123" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 K8s Service
-(http://syncguard-ai-agent-svc)</t>
+(http://syncflow-ai-agent-svc)</t>
         </is>
       </c>
       <c r="G40" s="122" t="inlineStr">
@@ -7869,8 +7869,8 @@
       </c>
       <c r="D41" s="45" t="inlineStr">
         <is>
-          <t>EKS 업무서버(syncguard-be-server)
-EKS 대외연계(syncguard-api-server)</t>
+          <t>EKS 업무서버(syncflow-be-server)
+EKS 대외연계(syncflow-api-server)</t>
         </is>
       </c>
       <c r="E41" s="122" t="inlineStr">
@@ -7881,7 +7881,7 @@
       <c r="F41" s="123" t="inlineStr">
         <is>
           <t>RDS PostgreSQL 16
-(hb_syncguard_ai_prd)</t>
+(hb_syncflow_ai_prd)</t>
         </is>
       </c>
       <c r="G41" s="122" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="I41" s="123" t="inlineStr">
         <is>
-          <t>[업무BE·연계API ➔ DB] 심의 마스터, 웹 영상 보정 장면 메타, 골든셋, 감사로그(WORM) 트랜잭션 R/W 및 하이브리드 검색</t>
+          <t>[업무BE·연계API ➔ DB] 검증 마스터, 웹 영상 보정 장면 메타, 골든셋, 감사로그(WORM) 트랜잭션 R/W 및 하이브리드 검색</t>
         </is>
       </c>
       <c r="J41" s="124" t="n">
@@ -7926,8 +7926,8 @@
       </c>
       <c r="D42" s="45" t="inlineStr">
         <is>
-          <t>EKS AI 에이전트(syncguard-ai-agent)
-EKS 배치 워커(syncguard-batch-server)</t>
+          <t>EKS AI 에이전트(syncflow-ai-agent)
+EKS 배치 워커(syncflow-batch-server)</t>
         </is>
       </c>
       <c r="E42" s="122" t="inlineStr">
@@ -7938,7 +7938,7 @@
       <c r="F42" s="123" t="inlineStr">
         <is>
           <t>RDS PostgreSQL 16 + pgvector
-(hb_syncguard_ai_prd)</t>
+(hb_syncflow_ai_prd)</t>
         </is>
       </c>
       <c r="G42" s="122" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="I42" s="123" t="inlineStr">
         <is>
-          <t>[Agent·Batch ➔ DB] 동시 4건 대기열(QUEUED) 폴링, AI 판정·피크프레임 결과 저장, pgvector(1536d HNSW) RAG 검색 및 색인</t>
+          <t>[Agent·Batch ➔ DB] 동시 4건 대기열(QUEUED) 폴링, AI 판정·도면스냅샷 결과 저장, pgvector(1536d HNSW) RAG 검색 및 색인</t>
         </is>
       </c>
       <c r="J42" s="124" t="n">
@@ -7994,7 +7994,7 @@
       <c r="F43" s="123" t="inlineStr">
         <is>
           <t>AWS S3 Endpoint
-s3.ap-northeast-2.amazonaws.com (ap-syncguard-ai-prd)</t>
+s3.ap-northeast-2.amazonaws.com (ap-syncflow-ai-prd)</t>
         </is>
       </c>
       <c r="G43" s="122" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="I43" s="123" t="inlineStr">
         <is>
-          <t>[EKS ➔ S3 스토리지] 300MB 시안·동영상 원본, AI 추출 피크프레임 및 웹 보정 장면, 리포트 저장 (업로드 시 Intelligent-Tiering 자동 적용)</t>
+          <t>[EKS ➔ S3 스토리지] 300MB 계약·도서·설계도면 원본, AI 추출 도면스냅샷 및 웹 보정 장면, 리포트 저장 (업로드 시 Intelligent-Tiering 자동 적용)</t>
         </is>
       </c>
       <c r="J43" s="124" t="n">
@@ -8040,7 +8040,7 @@
       <c r="D44" s="45" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 Pod
-(syncguard-ai-agent :18083)</t>
+(syncflow-ai-agent :18083)</t>
         </is>
       </c>
       <c r="E44" s="122" t="inlineStr">
@@ -8050,8 +8050,8 @@
       </c>
       <c r="F44" s="123" t="inlineStr">
         <is>
-          <t>https://*.apigw.ntruss.com
-(네이버 클라우드 Clova OCR Gateway)</t>
+          <t>https://ocr-api.hanbitglobal.internal
+(사내 표준 Enterprise Vision OCR Gateway)</t>
         </is>
       </c>
       <c r="G44" s="122" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="I44" s="123" t="inlineStr">
         <is>
-          <t>[대외 Outbound - 네이버 OCR] 시안 이미지·배너·영상 피크프레임/보정장면 및 하단 미세각주 고해상도 한글 OCR 추출 (연구소 기계약 API)</t>
+          <t>[대외 Outbound - 엔터프라이즈 비전 OCR] 계약·도서 이미지·배너·영상 도면스냅샷/보정장면 및 하단 특약주석 고해상도 한글 OCR 추출 (연구소 기계약 API)</t>
         </is>
       </c>
       <c r="J44" s="124" t="n">
@@ -8097,7 +8097,7 @@
       <c r="D45" s="45" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 Pod
-(syncguard-ai-agent :18083)</t>
+(syncflow-ai-agent :18083)</t>
         </is>
       </c>
       <c r="E45" s="122" t="inlineStr">
@@ -8154,7 +8154,7 @@
       <c r="D46" s="45" t="inlineStr">
         <is>
           <t>EKS AI 에이전트 Pod
-(syncguard-ai-agent :18083)</t>
+(syncflow-ai-agent :18083)</t>
         </is>
       </c>
       <c r="E46" s="122" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="I46" s="123" t="inlineStr">
         <is>
-          <t>[대외 Outbound - 상용 LLM] 기업용 비학습 Claude 3.5 Sonnet 기반 문구별 규제·실증 교차 판정 및 대체 문구 생성</t>
+          <t>[대외 Outbound - 상용 LLM] 기업용 비학습 Claude 3.5 Sonnet 기반 조항별 규제·시험검증 교차 판정 및 대체 조항 생성</t>
         </is>
       </c>
       <c r="J46" s="124" t="n">
@@ -8210,8 +8210,8 @@
       </c>
       <c r="D47" s="45" t="inlineStr">
         <is>
-          <t>EKS 대외연계(syncguard-api-server)
-EKS 업무서버(syncguard-be-server)</t>
+          <t>EKS 대외연계(syncflow-api-server)
+EKS 업무서버(syncflow-be-server)</t>
         </is>
       </c>
       <c r="E47" s="122" t="inlineStr">
@@ -8221,8 +8221,8 @@
       </c>
       <c r="F47" s="123" t="inlineStr">
         <is>
-          <t>https://mkthub-api.hanbitglobal.com
-(마케팅허브 사내 연계 API 서버)</t>
+          <t>https://srm-api.hanbitglobal.com
+(전자구매포털 사내 연계 API 서버)</t>
         </is>
       </c>
       <c r="G47" s="122" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="I47" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 마케팅허브 콜백] AI 1차 심의 완료 및 RA 최종 확정 결과(HTML 리포트 요약 + JSON) 마케팅허브 웹훅(Callback) 송신</t>
+          <t>[사내 Outbound - 전자구매포털 콜백] AI 1차 검증 완료 및 QA 최종 확정 결과(HTML 리포트 요약 + JSON) 전자구매포털 웹훅(Callback) 송신</t>
         </is>
       </c>
       <c r="J47" s="124" t="n">
@@ -8267,8 +8267,8 @@
       </c>
       <c r="D48" s="45" t="inlineStr">
         <is>
-          <t>EKS 대외연계(syncguard-api-server)
-EKS 배치 워커(syncguard-batch-server)</t>
+          <t>EKS 대외연계(syncflow-api-server)
+EKS 배치 워커(syncflow-batch-server)</t>
         </is>
       </c>
       <c r="E48" s="122" t="inlineStr">
@@ -8278,8 +8278,8 @@
       </c>
       <c r="F48" s="123" t="inlineStr">
         <is>
-          <t>mkthub-db.hanbitglobal.com
-(마케팅허브 DB 및 첨부파일 서버)</t>
+          <t>srm-db.hanbitglobal.com
+(전자구매포털 DB 및 첨부파일 서버)</t>
         </is>
       </c>
       <c r="G48" s="122" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="I48" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 마케팅허브 DB/파일] 마케팅허브 심의 의뢰 메타데이터 조회 및 대용량 첨부 시안·영상 파일 다운로드 연동</t>
+          <t>[사내 Outbound - 전자구매포털 DB/파일] 전자구매포털 검증 요청 메타데이터 조회 및 대용량 첨부 계약·도서·영상 파일 다운로드 연동</t>
         </is>
       </c>
       <c r="J48" s="124" t="n">
@@ -8324,8 +8324,8 @@
       </c>
       <c r="D49" s="45" t="inlineStr">
         <is>
-          <t>EKS 배치 워커(syncguard-batch-server)
-EKS 업무서버(syncguard-be-server)</t>
+          <t>EKS 배치 워커(syncflow-batch-server)
+EKS 업무서버(syncflow-be-server)</t>
         </is>
       </c>
       <c r="E49" s="122" t="inlineStr">
@@ -8335,8 +8335,8 @@
       </c>
       <c r="F49" s="123" t="inlineStr">
         <is>
-          <t>https://productlab-core.hanbitglobal.com
-(프로덕트랩 사내 연계 API 서버)</t>
+          <t>https://plmnexus-core.hanbitglobal.com
+(피엘엠넥서스 사내 연계 API 서버)</t>
         </is>
       </c>
       <c r="G49" s="122" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="I49" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 프로덕트랩 API] 매일 02:00 일배치 전성분·배합한도·임상보고서 증분 수집 및 심의 시 실시간 단건 조회</t>
+          <t>[사내 Outbound - 피엘엠넥서스 API] 매일 02:00 일배치 자재BOM·유해물질한도·신뢰성보고서 증분 수집 및 검증 시 실시간 단건 조회</t>
         </is>
       </c>
       <c r="J49" s="124" t="n">
@@ -8382,7 +8382,7 @@
       <c r="D50" s="45" t="inlineStr">
         <is>
           <t>EKS 배치 워커 Pod
-(syncguard-batch-server :18084)</t>
+(syncflow-batch-server :18084)</t>
         </is>
       </c>
       <c r="E50" s="122" t="inlineStr">
@@ -8392,8 +8392,8 @@
       </c>
       <c r="F50" s="123" t="inlineStr">
         <is>
-          <t>productlab-db.hanbitglobal.com
-(프로덕트랩 실증 DB 뷰)</t>
+          <t>plmnexus-db.hanbitglobal.com
+(피엘엠넥서스 시험검증 DB 뷰)</t>
         </is>
       </c>
       <c r="G50" s="122" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="I50" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 프로덕트랩 DB] 프로덕트랩 전성분·처방·기술원 인체적용시험 실증보고서 뷰(View) 일배치 대량 동기화</t>
+          <t>[사내 Outbound - 피엘엠넥서스 DB] 피엘엠넥서스 자재BOM·설계사양·기술원 공인신뢰성시험 시험검증보고서 뷰(View) 일배치 대량 동기화</t>
         </is>
       </c>
       <c r="J50" s="124" t="n">
@@ -8438,8 +8438,8 @@
       </c>
       <c r="D51" s="45" t="inlineStr">
         <is>
-          <t>EKS 업무서버(syncguard-be-server)
-EKS 대외연계(syncguard-api-server)</t>
+          <t>EKS 업무서버(syncflow-be-server)
+EKS 대외연계(syncflow-api-server)</t>
         </is>
       </c>
       <c r="E51" s="122" t="inlineStr">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="I51" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - SSO/IAM] BO 통합 웹 콘솔(:3104) 접속 시 SAML 2.0 / OIDC 인증 검증 및 역할별(RA·마케터·관리자) 권한 조회</t>
+          <t>[사내 Outbound - SSO/IAM] BO 통합 웹 콘솔(:3104) 접속 시 SAML 2.0 / OIDC 인증 검증 및 역할별(QA·구매담당자·관리자) 권한 조회</t>
         </is>
       </c>
       <c r="J51" s="124" t="n">
@@ -8496,7 +8496,7 @@
       <c r="D52" s="45" t="inlineStr">
         <is>
           <t>EKS 메인 업무서버 Pod
-(syncguard-be-server :18080)</t>
+(syncflow-be-server :18080)</t>
         </is>
       </c>
       <c r="E52" s="122" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="I52" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 메일발송] 실증자료 미비 시 연구소 담당자 대상 실증 요청 메일 발송 및 심의 완료 알림 발송</t>
+          <t>[사내 Outbound - 메일발송] 시험성적서 미비 시 연구소 담당자 대상 시험검증 요청 메일 발송 및 검증 완료 알림 발송</t>
         </is>
       </c>
       <c r="J52" s="124" t="n">
@@ -8553,7 +8553,7 @@
       <c r="D53" s="45" t="inlineStr">
         <is>
           <t>EKS 배치 워커 Pod
-(syncguard-batch-server :18084)</t>
+(syncflow-batch-server :18084)</t>
         </is>
       </c>
       <c r="E53" s="122" t="inlineStr">
@@ -8564,7 +8564,7 @@
       <c r="F53" s="123" t="inlineStr">
         <is>
           <t>https://ktlemon-gw.hanbitglobal.com
-([Option] KT 레몬 연계 게이트웨이)</t>
+([Option] HB-Monitor 연계 게이트웨이)</t>
         </is>
       </c>
       <c r="G53" s="122" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="I53" s="123" t="inlineStr">
         <is>
-          <t>[사내 Outbound - 선택 과업] 매일 02:30 식약처 표시·광고 공정화법·고시·가이드라인 개정본(Diff) 자동 수집 연동</t>
+          <t>[사내 Outbound - 선택 과업] 매일 02:30 공정위·표준원 하도급거래 공정화법·고시·가이드라인 개정본(Diff) 자동 수집 연동</t>
         </is>
       </c>
       <c r="J53" s="124" t="n">
@@ -9063,7 +9063,7 @@
       <c r="I2" s="60" t="inlineStr">
         <is>
           <t>• 포트 8000 허용 (ALB → tox-backend 내부 통신)
-• pip / UV 패키지 매니저 사전 설치 요청</t>
+• pip / UV 도면도면도면패키지 매니저 사전 설치 요청</t>
         </is>
       </c>
       <c r="J2" s="60" t="n"/>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="I3" s="60" t="inlineStr">
         <is>
-          <t>• pip / UV 패키지 매니저 사전 설치 요청
+          <t>• pip / UV 도면도면도면패키지 매니저 사전 설치 요청
 • Playwright chromium 브라우저 바이너리 설치 필요
 • 아웃바운드 :443 허용
   - AI Studio API Gateway (LLM 추출)
@@ -10292,8 +10292,8 @@
       <c r="B2" s="61" t="inlineStr">
         <is>
           <t>EKS 컨테이너
-(syncguard-fe-web &amp;
-syncguard-be-server)</t>
+(syncflow-fe-web &amp;
+syncflow-be-server)</t>
         </is>
       </c>
       <c r="C2" s="61" t="inlineStr">
@@ -10314,13 +10314,13 @@
       </c>
       <c r="F2" s="60" t="inlineStr">
         <is>
-          <t>• 통합 웹(Client/fe :3104): Node 20, Vue 3 / React 정적 서빙 + 웹 동영상 재생·특정화면 멈춤 장면 추가 및 AI 생성 장면 편집/삭제 UI
-• 메인 업무서버(server-be :18080): OpenJDK 21, Spring Boot 3.3.5 (심의 워크플로우, 과거 상충탐지, 골든셋, 백오피스, BO➔Agent 호출)</t>
+          <t>• 통합 웹(Client/fe :3104): Node 20, Vue 3 / React 정적 서빙 + 웹 설계도면 재생·특정화면 멈춤 장면 추가 및 AI 생성 장면 편집/삭제 UI
+• 메인 업무서버(server-be :18080): OpenJDK 21, Spring Boot 3.3.5 (검증 워크플로우, 과거 상충탐지, 골든셋, 백오피스, BO➔Agent 호출)</t>
         </is>
       </c>
       <c r="G2" s="61" t="inlineStr">
         <is>
-          <t>AP 기본 제공 타입
+          <t>HB 표준 제공 타입
 (성능테스트 OOM 시
 증설 요청)</t>
         </is>
@@ -10329,20 +10329,20 @@
         <is>
           <t>int
 [BO 전용 ALB 물리분리]
-(syncguard-ai-bo-prv-alb-dev)</t>
+(syncflow-ai-bo-prv-alb-dev)</t>
         </is>
       </c>
       <c r="I2" s="60" t="inlineStr">
         <is>
           <t>• [물리적 ALB 분리 ① - BO 전용 ALB] 사용자대역(사내 PC/VPN :443) 오픈 ➔ 통합웹(:3104) 및 업무서버(:18080) 라우팅
-• [BO ➔ Agent 호출] 웹 화면에서 영상 장면 추가/편집/삭제 후 재분석 요청 시 업무서버(:18080)에서 EKS K8s Service(http://syncguard-ai-agent-svc:18083)로 AI 에이전트 호출
-• 사내 Outbound :443/587 허용: SSO/IAM(sso.hanbitglobal.com), 마케팅허브, 프로덕트랩, SMTP(:587)</t>
+• [BO ➔ Agent 호출] 웹 화면에서 영상 장면 추가/편집/삭제 후 재분석 요청 시 업무서버(:18080)에서 EKS K8s Service(http://syncflow-ai-agent-svc:18083)로 AI 에이전트 호출
+• 사내 Outbound :443/587 허용: SSO/IAM(sso.hanbitglobal.com), 전자구매포털, 피엘엠넥서스, SMTP(:587)</t>
         </is>
       </c>
       <c r="J2" s="61" t="inlineStr">
         <is>
           <t>BO 전용 ALB 물리 분리
-AP 기본 스펙 우선 적용</t>
+HB 표준 스펙 우선 적용</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10355,7 @@
       <c r="B3" s="61" t="inlineStr">
         <is>
           <t>EKS 컨테이너
-(syncguard-api-server)</t>
+(syncflow-api-server)</t>
         </is>
       </c>
       <c r="C3" s="61" t="inlineStr">
@@ -10377,13 +10377,13 @@
       <c r="F3" s="60" t="inlineStr">
         <is>
           <t>• 대외연계 API(server-api :18085): OpenJDK 21, Spring Boot 3.3.5
-• 마케팅허브 심의 의뢰 수신 및 결과(HTML/JSON) 웹훅 콜백 회신
-• 300MB 대용량 시안·동영상 S3 멀티파트 스트리밍 업로드 전담</t>
+• 전자구매포털 검증 요청 수신 및 결과(HTML/JSON) 웹훅 콜백 회신
+• 300MB 대용량 계약·도서·설계도면 S3 멀티파트 스트리밍 업로드 전담</t>
         </is>
       </c>
       <c r="G3" s="61" t="inlineStr">
         <is>
-          <t>AP 기본 제공 타입
+          <t>HB 표준 제공 타입
 (성능테스트 OOM 시
 증설 요청)</t>
         </is>
@@ -10392,19 +10392,19 @@
         <is>
           <t>int
 [대외연계 ALB 물리분리]
-(syncguard-ai-api-prv-alb-dev)</t>
+(syncflow-ai-api-prv-alb-dev)</t>
         </is>
       </c>
       <c r="I3" s="60" t="inlineStr">
         <is>
-          <t>• [물리적 ALB 분리 ② - 대외연계 전용 ALB] 마케팅허브(MarketingHub) 서버 IP만 단독 오픈(:443)하여 접근 통제 분리 (일반 사용자대역 접근 차단)
-• [대외연계 ➔ Agent 호출] 심의 의뢰 접수 시 대외연계 서버(:18085)에서 EKS K8s Service(http://syncguard-ai-agent-svc:18083)를 통해 AI 에이전트 호출
+          <t>• [물리적 ALB 분리 ② - 대외연계 전용 ALB] 전자구매포털(SRM-Portal) 서버 IP만 단독 오픈(:443)하여 접근 통제 분리 (일반 사용자대역 접근 차단)
+• [대외연계 ➔ Agent 호출] 검증 요청 접수 시 대외연계 서버(:18085)에서 EKS K8s Service(http://syncflow-ai-agent-svc:18083)를 통해 AI 에이전트 호출
 • 300MB 대용량 업로드 대응: ALB Idle Timeout 300초, Max Body Size 350MB 설정</t>
         </is>
       </c>
       <c r="J3" s="61" t="inlineStr">
         <is>
-          <t>마케팅허브만 오픈(접근통제)
+          <t>전자구매포털만 오픈(접근통제)
 대외연계 ALB 물리 분리</t>
         </is>
       </c>
@@ -10418,12 +10418,12 @@
       <c r="B4" s="61" t="inlineStr">
         <is>
           <t>EKS 컨테이너
-(syncguard-ai-agent)</t>
+(syncflow-ai-agent)</t>
         </is>
       </c>
       <c r="C4" s="61" t="inlineStr">
         <is>
-          <t>AI 멀티모달 심의
+          <t>AI 멀티모달 검증
 에이전트 워커(:18083)
 [동시 4건 큐]</t>
         </is>
@@ -10440,14 +10440,14 @@
       <c r="F4" s="60" t="inlineStr">
         <is>
           <t>• Python 3.11, FastAPI, Uvicorn (:18083)
-• OpenCV / FFmpeg: 영상 피크프레임·미세각주 1차 자동추출 + 웹 보정 장면 재분석
-• 네이버 클로바 OCR API 연동 + PaddleOCR 폴백
+• OpenCV / FFmpeg: 도면 핵심규격·특약주석 1차 자동추출 + 웹 보정 장면 재분석
+• 엔터프라이즈 비전 OCR API 연동 + PaddleOCR 폴백
 • 기업용 비학습 LLM 연동 및 1536차원 하이브리드 RAG 엔진</t>
         </is>
       </c>
       <c r="G4" s="61" t="inlineStr">
         <is>
-          <t>AP 기본 제공 타입
+          <t>HB 표준 제공 타입
 (성능테스트 OOM 시
 증설 요청)</t>
         </is>
@@ -10461,16 +10461,16 @@
       </c>
       <c r="I4" s="60" t="inlineStr">
         <is>
-          <t>• [EKS K8s Service 통신] 업무서버(server-be :18080) 및 대외연계 서버(server-api :18085)에서 K8s Service(http://syncguard-ai-agent-svc:18083)로 호출
+          <t>• [EKS K8s Service 통신] 업무서버(server-be :18080) 및 대외연계 서버(server-api :18085)에서 K8s Service(http://syncflow-ai-agent-svc:18083)로 호출
 • [동시성 제어] asyncio.Semaphore(4) 최대 4건 동시 처리 + 초과분 DB 대기열(QUEUED) 순차 폴링
 • [대외 Outbound :443 방화벽 오픈 필수]
-  - 네이버 클로바 OCR: https://*.apigw.ntruss.com (:443)
+  - 엔터프라이즈 비전 OCR: https://ocr-api.hanbitglobal.internal (:443)
   - 상용 LLM/임베딩: https://api.openai.com, https://api.anthropic.com (:443)</t>
         </is>
       </c>
       <c r="J4" s="61" t="inlineStr">
         <is>
-          <t>AP 기본 제공 타입 적용
+          <t>HB 표준 제공 타입 적용
 (OOM 발생 시 증설 요청)</t>
         </is>
       </c>
@@ -10484,7 +10484,7 @@
       <c r="B5" s="61" t="inlineStr">
         <is>
           <t>EKS 컨테이너
-(syncguard-batch-server)</t>
+(syncflow-batch-server)</t>
         </is>
       </c>
       <c r="C5" s="61" t="inlineStr">
@@ -10505,13 +10505,13 @@
       <c r="F5" s="60" t="inlineStr">
         <is>
           <t>• OpenJDK 21, Spring Boot 3.3.5 + Spring Scheduler (:18084)
-• 매일 02:00 프로덕트랩(ProductLab) 전성분·배합한도·임상보고서 증분 수집
-• [Option] 매일 02:30 KT 레몬 식약처 법령·가이드라인 개정본(Diff) 수집</t>
+• 매일 02:00 피엘엠넥서스(PLM-Nexus) 자재BOM·유해물질한도·신뢰성보고서 증분 수집
+• [Option] 매일 02:30 HB-Monitor 공정위·표준원 법령·가이드라인 개정본(Diff) 수집</t>
         </is>
       </c>
       <c r="G5" s="61" t="inlineStr">
         <is>
-          <t>AP 기본 제공 타입
+          <t>HB 표준 제공 타입
 (성능테스트 OOM 시
 증설 요청)</t>
         </is>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="I5" s="60" t="inlineStr">
         <is>
-          <t>• 사내 Outbound 오픈: 프로덕트랩 API(https://productlab-core.hanbitglobal.com:443) 및 DB(:1521/5432), 마케팅허브 DB, [Option] KT 레몬(https://ktlemon-gw.hanbitglobal.com:443)
+          <t>• 사내 Outbound 오픈: 피엘엠넥서스 API(https://plmnexus-core.hanbitglobal.com:443) 및 DB(:1521/5432), 전자구매포털 DB, [Option] HB-Monitor(https://ktlemon-gw.hanbitglobal.com:443)
 • 신규 수집 문서 청킹·벡터 색인 시 EKS K8s Service로 AI 에이전트(:18083) 호출</t>
         </is>
       </c>
@@ -10563,7 +10563,7 @@
       <c r="F6" s="60" t="inlineStr">
         <is>
           <t>• AWS RDS for PostgreSQL 16 (Port: 5432)
-• DB명: hb_syncguard_ai_dev (단일 인스턴스 내 서비스·RAG 25개 테이블 통합)
+• DB명: hb_syncflow_ai_dev (단일 인스턴스 내 서비스·RAG 25개 테이블 통합)
 • 필수 확장: CREATE EXTENSION IF NOT EXISTS vector; (pgvector 0.7+)</t>
         </is>
       </c>
@@ -10589,7 +10589,7 @@
       <c r="J6" s="61" t="inlineStr">
         <is>
           <t>서비스+pgvector 통합
-AP 기본 스펙 우선 구성</t>
+HB 표준 스펙 우선 구성</t>
         </is>
       </c>
     </row>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="C7" s="61" t="inlineStr">
         <is>
-          <t>시안·영상 원본 / 보정장면
+          <t>계약·도서·영상 원본 / 보정장면
 / 리포트 보관</t>
         </is>
       </c>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="F7" s="60" t="inlineStr">
         <is>
-          <t>• 버킷명: ap-syncguard-ai-dev
+          <t>• 버킷명: ap-syncflow-ai-dev
 • 저장 타입: 업로드 시 "Intelligent-Tiering" 자동 적용
   (x-amz-storage-class: INTELLIGENT_TIERING)</t>
         </is>
@@ -10639,7 +10639,7 @@
       <c r="I7" s="60" t="inlineStr">
         <is>
           <t>• [인프라 리뷰 반영] 파일 보관주기가 명확하게 정해지지 않아 자동 패턴 분석을 통한 S3 보관비용 관리를 위해 업로드 시 "Intelligent-Tiering" 자동 적용
-• 300MB 시안·동영상 원본, AI 1차 자동추출 피크프레임 및 웹 사용자 보정 장면 이미지, 심의 리포트(HTML/PDF/Excel) 저장
+• 300MB 계약·도서·설계도면 원본, AI 1차 자동추출 도면스냅샷 및 웹 사용자 보정 장면 이미지, 검증 리포트(HTML/PDF/Excel) 저장
 • EKS Pod IAM Role(IRSA) Read/Write 권한 부여 (퍼블릭 액세스 차단, SSE-S3 암호화)</t>
         </is>
       </c>
@@ -10659,8 +10659,8 @@
       <c r="B8" s="61" t="inlineStr">
         <is>
           <t>EKS 컨테이너
-(syncguard-fe-web &amp;
-syncguard-be-server)</t>
+(syncflow-fe-web &amp;
+syncflow-be-server)</t>
         </is>
       </c>
       <c r="C8" s="61" t="inlineStr">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="G8" s="61" t="inlineStr">
         <is>
-          <t>AP 기본 제공 타입
+          <t>HB 표준 제공 타입
 (성능테스트 OOM 시
 증설 요청)</t>
         </is>
@@ -10696,20 +10696,20 @@
         <is>
           <t>int
 [BO 전용 ALB 물리분리]
-(syncguard-ai-bo-prv-alb-stg)</t>
+(syncflow-ai-bo-prv-alb-stg)</t>
         </is>
       </c>
       <c r="I8" s="60" t="inlineStr">
         <is>
           <t>• [물리적 ALB 분리 ① - BO 전용 ALB] 사용자대역(사내 PC/VPN :443) 오픈 ➔ 통합웹(:3104) 및 업무서버(:18080) 라우팅
-• [BO ➔ Agent 호출] 웹 화면에서 영상 장면 추가/편집/삭제 후 재분석 요청 시 업무서버(:18080)에서 EKS K8s Service(http://syncguard-ai-agent-svc:18083)로 AI 에이전트 호출
-• 사내 Outbound :443/587 허용: SSO/IAM(sso.hanbitglobal.com), 마케팅허브, 프로덕트랩, SMTP(:587)</t>
+• [BO ➔ Agent 호출] 웹 화면에서 영상 장면 추가/편집/삭제 후 재분석 요청 시 업무서버(:18080)에서 EKS K8s Service(http://syncflow-ai-agent-svc:18083)로 AI 에이전트 호출
+• 사내 Outbound :443/587 허용: SSO/IAM(sso.hanbitglobal.com), 전자구매포털, 피엘엠넥서스, SMTP(:587)</t>
         </is>
       </c>
       <c r="J8" s="61" t="inlineStr">
         <is>
           <t>BO 전용 ALB 물리 분리
-AP 기본 스펙 우선 적용</t>
+HB 표준 스펙 우선 적용</t>
         </is>
       </c>
     </row>
@@ -10722,7 +10722,7 @@
       <c r="B9" s="61" t="inlineStr">
         <is>
           <t>EKS 컨테이너
-(syncguard-api-server)</t>
+(syncflow-api-server)</t>
         </is>
       </c>
       <c r="C9" s="61" t="inlineStr">
@@ -10744,12 +10744,12 @@
       <c r="F9" s="60" t="inlineStr">
         <is>
           <t>DEV 동일
-(마케팅허브 검증계 연동)</t>
+(전자구매포털 검증계 연동)</t>
         </is>
       </c>
       <c r="G9" s="61" t="inlineStr">
         <is>
-          <t>AP 기본 제공 타입
+          <t>HB 표준 제공 타입
 (성능테스트 OOM 시
 증설 요청)</t>
         </is>
@@ -10758,19 +10758,19 @@
         <is>
           <t>int
 [대외연계 ALB 물리분리]
-(syncguard-ai-api-prv-alb-stg)</t>
+(syncflow-ai-api-prv-alb-stg)</t>
         </is>
       </c>
       <c r="I9" s="60" t="inlineStr">
         <is>
-          <t>• [물리적 ALB 분리 ② - 대외연계 전용 ALB] 마케팅허브(MarketingHub) 서버 IP만 단독 오픈(:443)하여 접근 통제 분리 (일반 사용자대역 접근 차단)
-• [대외연계 ➔ Agent 호출] 심의 의뢰 접수 시 대외연계 서버(:18085)에서 EKS K8s Service(http://syncguard-ai-agent-svc:18083)를 통해 AI 에이전트 호출
+          <t>• [물리적 ALB 분리 ② - 대외연계 전용 ALB] 전자구매포털(SRM-Portal) 서버 IP만 단독 오픈(:443)하여 접근 통제 분리 (일반 사용자대역 접근 차단)
+• [대외연계 ➔ Agent 호출] 검증 요청 접수 시 대외연계 서버(:18085)에서 EKS K8s Service(http://syncflow-ai-agent-svc:18083)를 통해 AI 에이전트 호출
 • 300MB 대용량 업로드 대응: ALB Idle Timeout 300초, Max Body Size 350MB 설정</t>
         </is>
       </c>
       <c r="J9" s="61" t="inlineStr">
         <is>
-          <t>마케팅허브만 오픈(접근통제)
+          <t>전자구매포털만 오픈(접근통제)
 대외연계 ALB 물리 분리</t>
         </is>
       </c>
@@ -10784,12 +10784,12 @@
       <c r="B10" s="61" t="inlineStr">
         <is>
           <t>EKS 컨테이너
-(syncguard-ai-agent)</t>
+(syncflow-ai-agent)</t>
         </is>
       </c>
       <c r="C10" s="61" t="inlineStr">
         <is>
-          <t>AI 멀티모달 심의
+          <t>AI 멀티모달 검증
 에이전트 워커(:18083)
 [동시 4건 큐]</t>
         </is>
@@ -10806,12 +10806,12 @@
       <c r="F10" s="60" t="inlineStr">
         <is>
           <t>DEV 동일
-(피크프레임/OCR 메모리 측정)</t>
+(도면스냅샷/OCR 메모리 측정)</t>
         </is>
       </c>
       <c r="G10" s="61" t="inlineStr">
         <is>
-          <t>AP 기본 제공 타입
+          <t>HB 표준 제공 타입
 (성능테스트 OOM 시
 증설 요청)</t>
         </is>
@@ -10825,16 +10825,16 @@
       </c>
       <c r="I10" s="60" t="inlineStr">
         <is>
-          <t>• [EKS K8s Service 통신] 업무서버(server-be :18080) 및 대외연계 서버(server-api :18085)에서 K8s Service(http://syncguard-ai-agent-svc:18083)로 호출
+          <t>• [EKS K8s Service 통신] 업무서버(server-be :18080) 및 대외연계 서버(server-api :18085)에서 K8s Service(http://syncflow-ai-agent-svc:18083)로 호출
 • [동시성 제어] asyncio.Semaphore(4) 최대 4건 동시 처리 + 초과분 DB 대기열(QUEUED) 순차 폴링
 • [대외 Outbound :443 방화벽 오픈 필수]
-  - 네이버 클로바 OCR: https://*.apigw.ntruss.com (:443)
+  - 엔터프라이즈 비전 OCR: https://ocr-api.hanbitglobal.internal (:443)
   - 상용 LLM/임베딩: https://api.openai.com, https://api.anthropic.com (:443)</t>
         </is>
       </c>
       <c r="J10" s="61" t="inlineStr">
         <is>
-          <t>AP 기본 제공 타입 적용
+          <t>HB 표준 제공 타입 적용
 (OOM 발생 시 증설 요청)</t>
         </is>
       </c>
@@ -10848,7 +10848,7 @@
       <c r="B11" s="61" t="inlineStr">
         <is>
           <t>EKS 컨테이너
-(syncguard-batch-server)</t>
+(syncflow-batch-server)</t>
         </is>
       </c>
       <c r="C11" s="61" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="G11" s="61" t="inlineStr">
         <is>
-          <t>AP 기본 제공 타입
+          <t>HB 표준 제공 타입
 (성능테스트 OOM 시
 증설 요청)</t>
         </is>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="I11" s="60" t="inlineStr">
         <is>
-          <t>• 사내 Outbound 오픈: 프로덕트랩 API(https://productlab-core.hanbitglobal.com:443) 및 DB(:1521/5432), 마케팅허브 DB, [Option] KT 레몬(https://ktlemon-gw.hanbitglobal.com:443)
+          <t>• 사내 Outbound 오픈: 피엘엠넥서스 API(https://plmnexus-core.hanbitglobal.com:443) 및 DB(:1521/5432), 전자구매포털 DB, [Option] HB-Monitor(https://ktlemon-gw.hanbitglobal.com:443)
 • 신규 수집 문서 청킹·벡터 색인 시 EKS K8s Service로 AI 에이전트(:18083) 호출</t>
         </is>
       </c>
@@ -10925,7 +10925,7 @@
       <c r="F12" s="60" t="inlineStr">
         <is>
           <t>• AWS RDS for PostgreSQL 16 (Port: 5432)
-• DB명: hb_syncguard_ai_stg (단일 인스턴스 내 서비스·RAG 25개 테이블 통합)
+• DB명: hb_syncflow_ai_stg (단일 인스턴스 내 서비스·RAG 25개 테이블 통합)
 • 필수 확장: CREATE EXTENSION IF NOT EXISTS vector; (pgvector 0.7+)</t>
         </is>
       </c>
@@ -10951,7 +10951,7 @@
       <c r="J12" s="61" t="inlineStr">
         <is>
           <t>서비스+pgvector 통합
-AP 기본 스펙 우선 구성</t>
+HB 표준 스펙 우선 구성</t>
         </is>
       </c>
     </row>
@@ -10969,7 +10969,7 @@
       </c>
       <c r="C13" s="61" t="inlineStr">
         <is>
-          <t>시안·영상 원본 / 보정장면
+          <t>계약·도서·영상 원본 / 보정장면
 / 리포트 보관</t>
         </is>
       </c>
@@ -10983,7 +10983,7 @@
       </c>
       <c r="F13" s="60" t="inlineStr">
         <is>
-          <t>• 버킷명: ap-syncguard-ai-stg
+          <t>• 버킷명: ap-syncflow-ai-stg
 • 저장 타입: 업로드 시 "Intelligent-Tiering" 자동 적용
   (x-amz-storage-class: INTELLIGENT_TIERING)</t>
         </is>
@@ -11001,7 +11001,7 @@
       <c r="I13" s="60" t="inlineStr">
         <is>
           <t>• [인프라 리뷰 반영] 파일 보관주기가 명확하게 정해지지 않아 자동 패턴 분석을 통한 S3 보관비용 관리를 위해 업로드 시 "Intelligent-Tiering" 자동 적용
-• 300MB 시안·동영상 원본, AI 1차 자동추출 피크프레임 및 웹 사용자 보정 장면 이미지, 심의 리포트(HTML/PDF/Excel) 저장
+• 300MB 계약·도서·설계도면 원본, AI 1차 자동추출 도면스냅샷 및 웹 사용자 보정 장면 이미지, 검증 리포트(HTML/PDF/Excel) 저장
 • EKS Pod IAM Role(IRSA) Read/Write 권한 부여 (퍼블릭 액세스 차단, SSE-S3 암호화)</t>
         </is>
       </c>
@@ -11021,8 +11021,8 @@
       <c r="B14" s="61" t="inlineStr">
         <is>
           <t>EKS 컨테이너
-(syncguard-fe-web &amp;
-syncguard-be-server)</t>
+(syncflow-fe-web &amp;
+syncflow-be-server)</t>
         </is>
       </c>
       <c r="C14" s="61" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="G14" s="61" t="inlineStr">
         <is>
-          <t>AP 기본 제공 타입
+          <t>HB 표준 제공 타입
 (성능테스트 OOM 시
 증설 요청)</t>
         </is>
@@ -11058,20 +11058,20 @@
         <is>
           <t>int
 [BO 전용 ALB 물리분리]
-(syncguard-ai-bo-prv-alb)</t>
+(syncflow-ai-bo-prv-alb)</t>
         </is>
       </c>
       <c r="I14" s="60" t="inlineStr">
         <is>
           <t>• [물리적 ALB 분리 ① - BO 전용 ALB] 사용자대역(사내 PC/VPN :443) 오픈 ➔ 통합웹(:3104) 및 업무서버(:18080) 라우팅
-• [BO ➔ Agent 호출] 웹 화면에서 영상 장면 추가/편집/삭제 후 재분석 요청 시 업무서버(:18080)에서 EKS K8s Service(http://syncguard-ai-agent-svc:18083)로 AI 에이전트 호출
-• 사내 Outbound :443/587 허용: SSO/IAM(sso.hanbitglobal.com), 마케팅허브, 프로덕트랩, SMTP(:587)</t>
+• [BO ➔ Agent 호출] 웹 화면에서 영상 장면 추가/편집/삭제 후 재분석 요청 시 업무서버(:18080)에서 EKS K8s Service(http://syncflow-ai-agent-svc:18083)로 AI 에이전트 호출
+• 사내 Outbound :443/587 허용: SSO/IAM(sso.hanbitglobal.com), 전자구매포털, 피엘엠넥서스, SMTP(:587)</t>
         </is>
       </c>
       <c r="J14" s="61" t="inlineStr">
         <is>
           <t>BO 전용 ALB 물리 분리
-AP 기본 스펙 우선 적용</t>
+HB 표준 스펙 우선 적용</t>
         </is>
       </c>
     </row>
@@ -11084,7 +11084,7 @@
       <c r="B15" s="61" t="inlineStr">
         <is>
           <t>EKS 컨테이너
-(syncguard-api-server)</t>
+(syncflow-api-server)</t>
         </is>
       </c>
       <c r="C15" s="61" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="G15" s="61" t="inlineStr">
         <is>
-          <t>AP 기본 제공 타입
+          <t>HB 표준 제공 타입
 (성능테스트 OOM 시
 증설 요청)</t>
         </is>
@@ -11120,19 +11120,19 @@
         <is>
           <t>int
 [대외연계 ALB 물리분리]
-(syncguard-ai-api-prv-alb)</t>
+(syncflow-ai-api-prv-alb)</t>
         </is>
       </c>
       <c r="I15" s="60" t="inlineStr">
         <is>
-          <t>• [물리적 ALB 분리 ② - 대외연계 전용 ALB] 마케팅허브(MarketingHub) 서버 IP만 단독 오픈(:443)하여 접근 통제 분리 (일반 사용자대역 접근 차단)
-• [대외연계 ➔ Agent 호출] 심의 의뢰 접수 시 대외연계 서버(:18085)에서 EKS K8s Service(http://syncguard-ai-agent-svc:18083)를 통해 AI 에이전트 호출
+          <t>• [물리적 ALB 분리 ② - 대외연계 전용 ALB] 전자구매포털(SRM-Portal) 서버 IP만 단독 오픈(:443)하여 접근 통제 분리 (일반 사용자대역 접근 차단)
+• [대외연계 ➔ Agent 호출] 검증 요청 접수 시 대외연계 서버(:18085)에서 EKS K8s Service(http://syncflow-ai-agent-svc:18083)를 통해 AI 에이전트 호출
 • 300MB 대용량 업로드 대응: ALB Idle Timeout 300초, Max Body Size 350MB 설정</t>
         </is>
       </c>
       <c r="J15" s="61" t="inlineStr">
         <is>
-          <t>마케팅허브만 오픈(접근통제)
+          <t>전자구매포털만 오픈(접근통제)
 대외연계 ALB 물리 분리</t>
         </is>
       </c>
@@ -11146,12 +11146,12 @@
       <c r="B16" s="61" t="inlineStr">
         <is>
           <t>EKS 컨테이너
-(syncguard-ai-agent)</t>
+(syncflow-ai-agent)</t>
         </is>
       </c>
       <c r="C16" s="61" t="inlineStr">
         <is>
-          <t>AI 멀티모달 심의
+          <t>AI 멀티모달 검증
 에이전트 워커(:18083)
 [동시 4건 큐]</t>
         </is>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="G16" s="61" t="inlineStr">
         <is>
-          <t>AP 기본 제공 타입
+          <t>HB 표준 제공 타입
 (성능테스트 OOM 시
 증설 요청)</t>
         </is>
@@ -11187,16 +11187,16 @@
       </c>
       <c r="I16" s="60" t="inlineStr">
         <is>
-          <t>• [EKS K8s Service 통신] 업무서버(server-be :18080) 및 대외연계 서버(server-api :18085)에서 K8s Service(http://syncguard-ai-agent-svc:18083)로 호출
+          <t>• [EKS K8s Service 통신] 업무서버(server-be :18080) 및 대외연계 서버(server-api :18085)에서 K8s Service(http://syncflow-ai-agent-svc:18083)로 호출
 • [동시성 제어] asyncio.Semaphore(4) 최대 4건 동시 처리 + 초과분 DB 대기열(QUEUED) 순차 폴링
 • [대외 Outbound :443 방화벽 오픈 필수]
-  - 네이버 클로바 OCR: https://*.apigw.ntruss.com (:443)
+  - 엔터프라이즈 비전 OCR: https://ocr-api.hanbitglobal.internal (:443)
   - 상용 LLM/임베딩: https://api.openai.com, https://api.anthropic.com (:443)</t>
         </is>
       </c>
       <c r="J16" s="61" t="inlineStr">
         <is>
-          <t>AP 기본 제공 타입 적용
+          <t>HB 표준 제공 타입 적용
 (OOM 발생 시 증설 요청)</t>
         </is>
       </c>
@@ -11210,7 +11210,7 @@
       <c r="B17" s="61" t="inlineStr">
         <is>
           <t>EKS 컨테이너
-(syncguard-batch-server)</t>
+(syncflow-batch-server)</t>
         </is>
       </c>
       <c r="C17" s="61" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="G17" s="61" t="inlineStr">
         <is>
-          <t>AP 기본 제공 타입
+          <t>HB 표준 제공 타입
 (성능테스트 OOM 시
 증설 요청)</t>
         </is>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="I17" s="60" t="inlineStr">
         <is>
-          <t>• 사내 Outbound 오픈: 프로덕트랩 API(https://productlab-core.hanbitglobal.com:443) 및 DB(:1521/5432), 마케팅허브 DB, [Option] KT 레몬(https://ktlemon-gw.hanbitglobal.com:443)
+          <t>• 사내 Outbound 오픈: 피엘엠넥서스 API(https://plmnexus-core.hanbitglobal.com:443) 및 DB(:1521/5432), 전자구매포털 DB, [Option] HB-Monitor(https://ktlemon-gw.hanbitglobal.com:443)
 • 신규 수집 문서 청킹·벡터 색인 시 EKS K8s Service로 AI 에이전트(:18083) 호출</t>
         </is>
       </c>
@@ -11287,7 +11287,7 @@
       <c r="F18" s="60" t="inlineStr">
         <is>
           <t>• AWS RDS for PostgreSQL 16 (Port: 5432)
-• DB명: hb_syncguard_ai_prd (단일 인스턴스 내 서비스·RAG 25개 테이블 통합)
+• DB명: hb_syncflow_ai_prd (단일 인스턴스 내 서비스·RAG 25개 테이블 통합)
 • 필수 확장: CREATE EXTENSION IF NOT EXISTS vector; (pgvector 0.7+)</t>
         </is>
       </c>
@@ -11313,7 +11313,7 @@
       <c r="J18" s="61" t="inlineStr">
         <is>
           <t>서비스+pgvector 통합
-AP 기본 스펙 우선 구성</t>
+HB 표준 스펙 우선 구성</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="C19" s="61" t="inlineStr">
         <is>
-          <t>시안·영상 원본 / 보정장면
+          <t>계약·도서·영상 원본 / 보정장면
 / 리포트 보관</t>
         </is>
       </c>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="F19" s="60" t="inlineStr">
         <is>
-          <t>• 버킷명: ap-syncguard-ai-prd
+          <t>• 버킷명: ap-syncflow-ai-prd
 • 저장 타입: 업로드 시 "Intelligent-Tiering" 자동 적용
   (x-amz-storage-class: INTELLIGENT_TIERING)</t>
         </is>
@@ -11363,7 +11363,7 @@
       <c r="I19" s="60" t="inlineStr">
         <is>
           <t>• [인프라 리뷰 반영] 파일 보관주기가 명확하게 정해지지 않아 자동 패턴 분석을 통한 S3 보관비용 관리를 위해 업로드 시 "Intelligent-Tiering" 자동 적용
-• 300MB 시안·동영상 원본, AI 1차 자동추출 피크프레임 및 웹 사용자 보정 장면 이미지, 심의 리포트(HTML/PDF/Excel) 저장
+• 300MB 계약·도서·설계도면 원본, AI 1차 자동추출 도면스냅샷 및 웹 사용자 보정 장면 이미지, 검증 리포트(HTML/PDF/Excel) 저장
 • EKS Pod IAM Role(IRSA) Read/Write 권한 부여 (퍼블릭 액세스 차단, SSE-S3 암호화)</t>
         </is>
       </c>
